--- a/docs/qa/SooDaMate_QA_Report_2026-09-20_final.xlsx
+++ b/docs/qa/SooDaMate_QA_Report_2026-09-20_final.xlsx
@@ -15,8 +15,8 @@
     <sheet name="기존 pytest 회귀" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'테스트케이스'!$A$1:$M$160</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'결함·수정'!$A$1:$I$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'테스트케이스'!$A$1:$M$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'결함·수정'!$A$1:$I$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'웹↔앱 일치 점검'!$A$1:$D$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'테스트 못한 것·한계'!$A$1:$C$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'기존 pytest 회귀'!$A$1:$E$154</definedName>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6">
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -580,7 +580,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>98.2%</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>99.8%  (733/735 체크)</t>
+          <t>99.8%  (769/771 체크)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.0%</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>10 / 2 / 5</t>
+          <t>11 / 2 / 5</t>
         </is>
       </c>
     </row>
@@ -869,14 +869,14 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>탐색(디스커버)</t>
+          <t>계정</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>0</v>
@@ -896,14 +896,14 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>스와이프·매칭</t>
+          <t>탐색(디스커버)</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="6" t="n">
         <v>0</v>
@@ -923,14 +923,14 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>채팅·통화</t>
+          <t>스와이프·매칭</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>0</v>
@@ -950,14 +950,14 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>블라인드 채팅·AI매칭</t>
+          <t>채팅·통화</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28" s="6" t="n">
         <v>0</v>
@@ -977,14 +977,14 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>모먼트</t>
+          <t>블라인드 채팅·AI매칭</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D29" s="6" t="n">
         <v>0</v>
@@ -1004,14 +1004,14 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>커플 스토리</t>
+          <t>모먼트</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="6" t="n">
         <v>0</v>
@@ -1031,14 +1031,14 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>결제</t>
+          <t>커플 스토리</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D31" s="6" t="n">
         <v>0</v>
@@ -1058,14 +1058,14 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>푸시·기기</t>
+          <t>결제</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D32" s="6" t="n">
         <v>0</v>
@@ -1085,14 +1085,14 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>계정</t>
+          <t>푸시·기기</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="6" t="n">
         <v>0</v>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D36" s="6" t="n">
         <v>0</v>
@@ -1224,19 +1224,19 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D38" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>95.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M160"/>
+  <dimension ref="A1:M168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="M54" s="10" t="n">
-        <v>13.29</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="55">
@@ -4499,37 +4499,37 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>DISC-001</t>
+          <t>AGE-001</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>탐색(디스커버)</t>
+          <t>계정</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Gender &amp; age matching</t>
+          <t>Under-18 age gate</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Only mutually-compatible people appear (gender interest + both age ranges)</t>
+          <t>App reports an under-18 birth date: the account is switched off for good and the same phone number cannot retry</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>5 users around one age, check /discovery/candidates</t>
+          <t>phone signup -&gt; age-restricted -&gt; token check -&gt; phone re-login</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>viewer sees the compatible person; does not see same-gender (not wanted), a person outside his age range, or someone whose own range excludes him</t>
+          <t>POST /account/age-restricted -&gt; 204; the old token stops working; logging in again with the same phone number -&gt; 403 (account disabled); anonymous call -&gt; 401/403</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>compatible shown: True; same gender hidden: True; outside viewer's age range hidden: True; self never shown: True</t>
+          <t>anonymous call refused: True; report under-18: 204; old token no longer works: True; same number cannot log in again: 403; detail: 'account disabled'</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
@@ -4542,55 +4542,49 @@
       </c>
       <c r="J56" s="10" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K56" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="L56" s="10" t="inlineStr">
-        <is>
-          <t>design note: a candidate whose own age preference excludes the viewer is still shown in Discover (only the viewer's own range is applied there; blind chat applies both)</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="10" t="n"/>
+      <c r="L56" s="10" t="inlineStr"/>
       <c r="M56" s="10" t="n">
-        <v>24.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>DISC-002</t>
+          <t>AGE-002</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>탐색(디스커버)</t>
+          <t>계정</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Deck hygiene</t>
+          <t>Under-18 age gate</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>Swiped people (like and pass) never reappear; no duplicates in the deck</t>
+          <t>Server independently rejects an under-18 birth date on profile creation; exactly 18 is accepted; birth date is mandatory to become discoverable</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>like one, pass one, refetch</t>
+          <t>PUT /profiles/me with ages 5, 17, 18; discovery/queue without a profile</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>after like/pass the users disappear; ids unique</t>
+          <t>17-year-old -&gt; 422; 18-year-old -&gt; 200; a profile-less account cannot browse or queue (400)</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>both visible first: True; no duplicate ids: 18; liked hidden: True; passed hidden: True</t>
+          <t>5 years old: 422; 17 years old: 422; no profile -&gt; discovery blocked: 400; no profile -&gt; blind queue blocked: 400; 18 years old: 200</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
@@ -4603,21 +4597,19 @@
       </c>
       <c r="J57" s="10" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K57" s="10" t="n">
-        <v>100</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="10" t="n"/>
       <c r="L57" s="10" t="inlineStr"/>
       <c r="M57" s="10" t="n">
-        <v>16.93</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>DISC-003</t>
+          <t>DISC-001</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -4627,27 +4619,27 @@
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Incognito</t>
+          <t>Gender &amp; age matching</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>Incognito users are hidden from the deck, and visible again when switched off</t>
+          <t>Only mutually-compatible people appear (gender interest + both age ranges)</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>toggle incognito on target</t>
+          <t>5 users around one age, check /discovery/candidates</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>hidden while is_incognito=True, present after off</t>
+          <t>viewer sees the compatible person; does not see same-gender (not wanted), a person outside his age range, or someone whose own range excludes him</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>visible: True; hidden when incognito: True; visible again: True</t>
+          <t>compatible shown: True; same gender hidden: True; outside viewer's age range hidden: True; self never shown: True</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
@@ -4660,21 +4652,25 @@
       </c>
       <c r="J58" s="10" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K58" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="L58" s="10" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="L58" s="10" t="inlineStr">
+        <is>
+          <t>design note: a candidate whose own age preference excludes the viewer is still shown in Discover (only the viewer's own range is applied there; blind chat applies both)</t>
+        </is>
+      </c>
       <c r="M58" s="10" t="n">
-        <v>15.24</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>DISC-004</t>
+          <t>DISC-002</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
@@ -4684,27 +4680,27 @@
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Distance</t>
+          <t>Deck hygiene</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>Distance limit, distance_km value, and travel mode relocating a user</t>
+          <t>Swiped people (like and pass) never reappear; no duplicates in the deck</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>lat/lng users + travel mode</t>
+          <t>like one, pass one, refetch</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>far user (Seoul vs New York) excluded within 50 km; near user shown with distance_km&lt;5; traveler to Seoul then appears</t>
+          <t>after like/pass the users disappear; ids unique</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>near shown: True; distance_km small: 0.5251195793958114; far hidden: True; traveler now shown: True; gone after travel cleared: True</t>
+          <t>both visible first: True; no duplicate ids: 18; liked hidden: True; passed hidden: True</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
@@ -4717,21 +4713,21 @@
       </c>
       <c r="J59" s="10" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K59" s="10" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="L59" s="10" t="inlineStr"/>
       <c r="M59" s="10" t="n">
-        <v>20.62</v>
+        <v>16.93</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>DISC-005</t>
+          <t>DISC-003</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -4741,27 +4737,27 @@
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Filters</t>
+          <t>Incognito</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>Basic filters narrow the deck (height / language / interests / verified only)</t>
+          <t>Incognito users are hidden from the deck, and visible again when switched off</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>PUT /profiles/me/basic-filters variants</t>
+          <t>toggle incognito on target</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>height 170-180 keeps 175cm only; interests_filter keeps the person with 'coffee'; languages_filter keeps ko speaker</t>
+          <t>hidden while is_incognito=True, present after off</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>175cm kept: True; 155cm dropped: True; interest filter keeps coffee: True; language filter keeps en speaker: True</t>
+          <t>visible: True; hidden when incognito: True; visible again: True</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
@@ -4782,13 +4778,13 @@
       </c>
       <c r="L60" s="10" t="inlineStr"/>
       <c r="M60" s="10" t="n">
-        <v>19.91</v>
+        <v>15.24</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>DISC-006</t>
+          <t>DISC-004</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -4798,27 +4794,27 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Data privacy</t>
+          <t>Distance</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>Candidate cards never leak private fields</t>
+          <t>Distance limit, distance_km value, and travel mode relocating a user</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
-          <t>inspect keys of candidate JSON</t>
+          <t>lat/lng users + travel mode</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>no email, phone, exact birth date, legal name, exact coordinates or password data in a candidate object</t>
+          <t>far user (Seoul vs New York) excluded within 50 km; near user shown with distance_km&lt;5; traveler to Seoul then appears</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>leaked keys: []; age is a number: 70; photo url is https: True</t>
+          <t>near shown: True; distance_km small: 0.5251195793958114; far hidden: True; traveler now shown: True; gone after travel cleared: True</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
@@ -4831,21 +4827,21 @@
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K61" s="10" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="L61" s="10" t="inlineStr"/>
       <c r="M61" s="10" t="n">
-        <v>10.26</v>
+        <v>20.62</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>DISC-007</t>
+          <t>DISC-005</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -4855,27 +4851,27 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Filters</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>limit parameter bounds</t>
+          <t>Basic filters narrow the deck (height / language / interests / verified only)</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>GET /discovery/candidates?limit=...</t>
+          <t>PUT /profiles/me/basic-filters variants</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>limit=0 and 51 -&gt; 422; limit=1 returns at most 1</t>
+          <t>height 170-180 keeps 175cm only; interests_filter keeps the person with 'coffee'; languages_filter keeps ko speaker</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>limit 0: 422; limit 51: 422; limit 1: True</t>
+          <t>175cm kept: True; 155cm dropped: True; interest filter keeps coffee: True; language filter keeps en speaker: True</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
@@ -4896,13 +4892,13 @@
       </c>
       <c r="L62" s="10" t="inlineStr"/>
       <c r="M62" s="10" t="n">
-        <v>6.06</v>
+        <v>19.91</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>DISC-008</t>
+          <t>DISC-006</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
@@ -4912,27 +4908,27 @@
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Ban filter</t>
+          <t>Data privacy</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>Banned users disappear from other people's decks</t>
+          <t>Candidate cards never leak private fields</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>ban via report action, refetch</t>
+          <t>inspect keys of candidate JSON</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>after an admin ban the user is no longer a candidate</t>
+          <t>no email, phone, exact birth date, legal name, exact coordinates or password data in a candidate object</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>visible before: True; hidden after ban: True</t>
+          <t>leaked keys: []; age is a number: 70; photo url is https: True</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
@@ -4953,13 +4949,13 @@
       </c>
       <c r="L63" s="10" t="inlineStr"/>
       <c r="M63" s="10" t="n">
-        <v>16.76</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>DISC-009</t>
+          <t>DISC-007</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -4969,27 +4965,27 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Premium filters</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Premium members can use advanced filters; free members get 402</t>
+          <t>limit parameter bounds</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>set premium via DB, PUT premium-filters</t>
+          <t>GET /discovery/candidates?limit=...</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>premium_until in future -&gt; premium-filters 200 and narrows the deck; expired premium -&gt; 402 again</t>
+          <t>limit=0 and 51 -&gt; 422; limit=1 returns at most 1</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>free user gated: 402; premium accepted: 200; non-smoker kept: True; smoker filtered: True; expired premium gated again: 402</t>
+          <t>limit 0: 422; limit 51: 422; limit 1: True</t>
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr">
@@ -5010,43 +5006,43 @@
       </c>
       <c r="L64" s="10" t="inlineStr"/>
       <c r="M64" s="10" t="n">
-        <v>19.37</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>MATCH-001</t>
+          <t>DISC-008</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>스와이프·매칭</t>
+          <t>탐색(디스커버)</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Mutual like</t>
+          <t>Ban filter</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>Like -&gt; no match; reciprocal like -&gt; match for both; visible in both /matches lists</t>
+          <t>Banned users disappear from other people's decks</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>A likes B, B likes A</t>
+          <t>ban via report action, refetch</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>first like matched=False; second like matched=True with match_id; both lists contain it with the other's name; like/match pushes recorded</t>
+          <t>after an admin ban the user is no longer a candidate</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>first like status: 200; first like matched: False; like push to B: True; second like matched: True; listed for A: True; listed for B: True; A sees B's name: 'QAm1F'; B sees A's name: 'QAm1M'; match pushes to both: True</t>
+          <t>visible before: True; hidden after ban: True</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
@@ -5067,43 +5063,43 @@
       </c>
       <c r="L65" s="10" t="inlineStr"/>
       <c r="M65" s="10" t="n">
-        <v>13.34</v>
+        <v>16.76</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>MATCH-002</t>
+          <t>DISC-009</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>스와이프·매칭</t>
+          <t>탐색(디스커버)</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Swipe validation</t>
+          <t>Premium filters</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Self-swipe, ghost user, duplicate swipe, and pass-then-like</t>
+          <t>Premium members can use advanced filters; free members get 402</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>swipe edge cases</t>
+          <t>set premium via DB, PUT premium-filters</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>self 400; unknown user 404; duplicate like idempotent 200; a pass never creates a match even if the other liked</t>
+          <t>premium_until in future -&gt; premium-filters 200 and narrows the deck; expired premium -&gt; 402 again</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>self: 400; ghost: 404; bad uuid: 422; duplicate like: 200; like after being passed -&gt; no match: False</t>
+          <t>free user gated: 402; premium accepted: 200; non-smoker kept: True; smoker filtered: True; expired premium gated again: 402</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
@@ -5124,13 +5120,13 @@
       </c>
       <c r="L66" s="10" t="inlineStr"/>
       <c r="M66" s="10" t="n">
-        <v>22.59</v>
+        <v>19.37</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>MATCH-003</t>
+          <t>MATCH-001</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
@@ -5140,27 +5136,27 @@
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Swipe limit</t>
+          <t>Mutual like</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>20 swipes per rolling 6h; the 21st is refused with 429 and a reset time; premium is unlimited</t>
+          <t>Like -&gt; no match; reciprocal like -&gt; match for both; visible in both /matches lists</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>23 users, 21 swipes</t>
+          <t>A likes B, B likes A</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>swipe-limit remaining counts down 20-&gt;0; 21st swipe 429 with resets_at; premium user unlimited=True</t>
+          <t>first like matched=False; second like matched=True with match_id; both lists contain it with the other's name; like/match pushes recorded</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr">
         <is>
-          <t>initial remaining: 20; remaining after 20: 0; resets_at present: True; 21st swipe: 429; 429 body has resets_at: True; premium unlimited: True; premium can keep swiping: 200</t>
+          <t>first like status: 200; first like matched: False; like push to B: True; second like matched: True; listed for A: True; listed for B: True; A sees B's name: 'QAm1F'; B sees A's name: 'QAm1M'; match pushes to both: True</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
@@ -5181,13 +5177,13 @@
       </c>
       <c r="L67" s="10" t="inlineStr"/>
       <c r="M67" s="10" t="n">
-        <v>109.56</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>MATCH-004</t>
+          <t>MATCH-002</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
@@ -5197,27 +5193,27 @@
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Super like</t>
+          <t>Swipe validation</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>1 free super like per day, then credits, else 402; target sees superliked_me</t>
+          <t>Self-swipe, ghost user, duplicate swipe, and pass-then-like</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>superlike x3</t>
+          <t>swipe edge cases</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>first superlike ok; second 402; after granting a credit ok again; target's candidate card and liked-me show superliked_me</t>
+          <t>self 400; unknown user 404; duplicate like idempotent 200; a pass never creates a match even if the other liked</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>free superlike: 200; second superlike blocked: 402; paid superlike: 200; credits consumed: 0; appears in liked-me: True; superliked_me flag: True</t>
+          <t>self: 400; ghost: 404; bad uuid: 422; duplicate like: 200; like after being passed -&gt; no match: False</t>
         </is>
       </c>
       <c r="H68" s="11" t="inlineStr">
@@ -5238,13 +5234,13 @@
       </c>
       <c r="L68" s="10" t="inlineStr"/>
       <c r="M68" s="10" t="n">
-        <v>22.08</v>
+        <v>22.59</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>MATCH-005</t>
+          <t>MATCH-003</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
@@ -5254,27 +5250,27 @@
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Liked-me list</t>
+          <t>Swipe limit</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>'Who liked me' lists likers and drops them once I respond</t>
+          <t>20 swipes per rolling 6h; the 21st is refused with 429 and a reset time; premium is unlimited</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>A likes B; B checks liked-me; B responds</t>
+          <t>23 users, 21 swipes</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>liker present; after I like back (match) or pass, they disappear</t>
+          <t>swipe-limit remaining counts down 20-&gt;0; 21st swipe 429 with resets_at; premium user unlimited=True</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>liker listed: True; removed after pass: True</t>
+          <t>initial remaining: 20; remaining after 20: 0; resets_at present: True; 21st swipe: 429; 429 body has resets_at: True; premium unlimited: True; premium can keep swiping: 200</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
@@ -5295,13 +5291,13 @@
       </c>
       <c r="L69" s="10" t="inlineStr"/>
       <c r="M69" s="10" t="n">
-        <v>12.49</v>
+        <v>109.56</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>MATCH-006</t>
+          <t>MATCH-004</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
@@ -5311,27 +5307,27 @@
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>First-message rule</t>
+          <t>Super like</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>Bumble rule: in a man/woman match only the woman may message first; error frame for the man; afterwards both can</t>
+          <t>1 free super like per day, then credits, else 402; target sees superliked_me</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>match + WebSocket messages</t>
+          <t>superlike x3</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>man's first message -&gt; error frame first_message_restricted and nothing stored; woman's message delivered; then man can reply; can_send_first_message flags correct</t>
+          <t>first superlike ok; second 402; after granting a credit ok again; target's candidate card and liked-me show superliked_me</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>man can_send_first_message: False; woman can_send_first_message: True; deadline set (24h): True; error frame: 'first_message_restricted'; woman delivered: 'woman first'; man reply delivered: 'man reply'; rejected message not stored: True; history: ['man reply', 'woman first']</t>
+          <t>free superlike: 200; second superlike blocked: 402; paid superlike: 200; credits consumed: 0; appears in liked-me: True; superliked_me flag: True</t>
         </is>
       </c>
       <c r="H70" s="11" t="inlineStr">
@@ -5352,13 +5348,13 @@
       </c>
       <c r="L70" s="10" t="inlineStr"/>
       <c r="M70" s="10" t="n">
-        <v>17.22</v>
+        <v>22.08</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>MATCH-007</t>
+          <t>MATCH-005</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
@@ -5368,27 +5364,27 @@
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Match expiry</t>
+          <t>Liked-me list</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>24h without a first message expires the match; history stays readable; sending is refused</t>
+          <t>'Who liked me' lists likers and drops them once I respond</t>
         </is>
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>backdate first_message_deadline</t>
+          <t>A likes B; B checks liked-me; B responds</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>after deadline passes: match is_active False, sending impossible, GET messages still 200</t>
+          <t>liker present; after I like back (match) or pass, they disappear</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>is_active after deadline: False; history readable: 200; no message stored: 0</t>
+          <t>liker listed: True; removed after pass: True</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
@@ -5409,13 +5405,13 @@
       </c>
       <c r="L71" s="10" t="inlineStr"/>
       <c r="M71" s="10" t="n">
-        <v>14.23</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>MATCH-008</t>
+          <t>MATCH-006</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -5425,27 +5421,27 @@
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Same-gender match</t>
+          <t>First-message rule</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>Same-gender (or 'other') matches are unrestricted from both sides</t>
+          <t>Bumble rule: in a man/woman match only the woman may message first; error frame for the man; afterwards both can</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>two men seeking men</t>
+          <t>match + WebSocket messages</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>no restriction flags; either side can message first</t>
+          <t>man's first message -&gt; error frame first_message_restricted and nothing stored; woman's message delivered; then man can reply; can_send_first_message flags correct</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>restricted: False; can send first: True; delivered: 'hey'</t>
+          <t>man can_send_first_message: False; woman can_send_first_message: True; deadline set (24h): True; error frame: 'first_message_restricted'; woman delivered: 'woman first'; man reply delivered: 'man reply'; rejected message not stored: True; history: ['man reply', 'woman first']</t>
         </is>
       </c>
       <c r="H72" s="11" t="inlineStr">
@@ -5466,13 +5462,13 @@
       </c>
       <c r="L72" s="10" t="inlineStr"/>
       <c r="M72" s="10" t="n">
-        <v>13.12</v>
+        <v>17.22</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>MATCH-009</t>
+          <t>MATCH-007</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
@@ -5482,27 +5478,27 @@
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Access control (IDOR)</t>
+          <t>Match expiry</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>A stranger cannot read or write another pair's match</t>
+          <t>24h without a first message expires the match; history stays readable; sending is refused</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>third user attacks a match</t>
+          <t>backdate first_message_deadline</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t>GET messages 404 for outsider; WS message to that match_id ignored; icebreaker / reveal / feedback endpoints refuse outsider</t>
+          <t>after deadline passes: match is_active False, sending impossible, GET messages still 200</t>
         </is>
       </c>
       <c r="G73" s="10" t="inlineStr">
         <is>
-          <t>read history: 404; injected message not stored: True; icebreaker refused: True; reveal request refused: True; feedback refused: True</t>
+          <t>is_active after deadline: False; history readable: 200; no message stored: 0</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
@@ -5523,13 +5519,13 @@
       </c>
       <c r="L73" s="10" t="inlineStr"/>
       <c r="M73" s="10" t="n">
-        <v>17.82</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>MATCH-010</t>
+          <t>MATCH-008</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -5539,27 +5535,27 @@
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>Icebreaker</t>
+          <t>Same-gender match</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>Icebreaker suggestion reflects shared interests / K-content / language exchange</t>
+          <t>Same-gender (or 'other') matches are unrestricted from both sides</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>3 pairs</t>
+          <t>two men seeking men</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>shared k-content -&gt; type shared_kcontent; shared interest -&gt; shared_interest; nothing shared -&gt; generic</t>
+          <t>no restriction flags; either side can message first</t>
         </is>
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>status: 200; type: 'shared_kcontent'; key: 'kdrama'; generic when nothing shared: 'generic'</t>
+          <t>restricted: False; can send first: True; delivered: 'hey'</t>
         </is>
       </c>
       <c r="H74" s="11" t="inlineStr">
@@ -5580,43 +5576,43 @@
       </c>
       <c r="L74" s="10" t="inlineStr"/>
       <c r="M74" s="10" t="n">
-        <v>29.15</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>CHAT-001</t>
+          <t>MATCH-009</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>채팅·통화</t>
+          <t>스와이프·매칭</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Realtime messaging</t>
+          <t>Access control (IDOR)</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>Two-way live chat, persistence, ordering, delivered/read state</t>
+          <t>A stranger cannot read or write another pair's match</t>
         </is>
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>WS chat between matched pair then read receipt</t>
+          <t>third user attacks a match</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>each message arrives on the peer socket with sender/content/time; history returns both in order; read event received by sender; read_at set in history</t>
+          <t>GET messages 404 for outsider; WS message to that match_id ignored; icebreaker / reveal / feedback endpoints refuse outsider</t>
         </is>
       </c>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>A gets msg 1: '안녕 1'; sender id: '538f7d14-41db-49b5-90d3-1d9c90ffdf00'; has sent_at + message_id: True; B gets msg 2: 'hello 2 😊'; B gets read event: 'read'; history order: ['안녕 1', 'hello 2 😊']; message from B marked read by A: True</t>
+          <t>read history: 404; injected message not stored: True; icebreaker refused: True; reveal request refused: True; feedback refused: True</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
@@ -5637,43 +5633,43 @@
       </c>
       <c r="L75" s="10" t="inlineStr"/>
       <c r="M75" s="10" t="n">
-        <v>14.08</v>
+        <v>17.82</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>CHAT-002</t>
+          <t>MATCH-010</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>채팅·통화</t>
+          <t>스와이프·매칭</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Image messages</t>
+          <t>Icebreaker</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>Send a REAL photo in chat: upload to R2, deliver, recipient downloads identical bytes</t>
+          <t>Icebreaker suggestion reflects shared interests / K-content / language exchange</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>chat presign + PUT + WS image</t>
+          <t>3 pairs</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>chat presign 200, R2 PUT 200, WS image message delivered with image_url, download hash equals upload, history shows message_type=image</t>
+          <t>shared k-content -&gt; type shared_kcontent; shared interest -&gt; shared_interest; nothing shared -&gt; generic</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>R2 PUT: 200; type: 'image'; image_url present: True; download: 200; bytes identical: '58b84aacfa05662b2a0fb64af8063aa89005c3829a875a0007aa53995d0c6951'; history has image message: True</t>
+          <t>status: 200; type: 'shared_kcontent'; key: 'kdrama'; generic when nothing shared: 'generic'</t>
         </is>
       </c>
       <c r="H76" s="11" t="inlineStr">
@@ -5694,13 +5690,13 @@
       </c>
       <c r="L76" s="10" t="inlineStr"/>
       <c r="M76" s="10" t="n">
-        <v>14.61</v>
+        <v>29.15</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>CHAT-003</t>
+          <t>CHAT-001</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
@@ -5710,27 +5706,27 @@
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>Input handling</t>
+          <t>Realtime messaging</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>Empty, whitespace-only, very long, emoji/RTL/HTML messages</t>
+          <t>Two-way live chat, persistence, ordering, delivered/read state</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>send edge-case messages</t>
+          <t>WS chat between matched pair then read receipt</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>empty and whitespace ignored (not stored); 5000-char message stored intact; emoji/RTL/HTML stored verbatim (clients escape); connection stays alive</t>
+          <t>each message arrives on the peer socket with sender/content/time; history returns both in order; read event received by sender; read_at set in history</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
         <is>
-          <t>long message delivered intact: '가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가</t>
+          <t>A gets msg 1: '안녕 1'; sender id: '538f7d14-41db-49b5-90d3-1d9c90ffdf00'; has sent_at + message_id: True; B gets msg 2: 'hello 2 😊'; B gets read event: 'read'; history order: ['안녕 1', 'hello 2 😊']; message from B marked read by A: True</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
@@ -5751,13 +5747,13 @@
       </c>
       <c r="L77" s="10" t="inlineStr"/>
       <c r="M77" s="10" t="n">
-        <v>17.48</v>
+        <v>14.08</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>CHAT-004</t>
+          <t>CHAT-002</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
@@ -5767,27 +5763,27 @@
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Push routing</t>
+          <t>Image messages</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>Push only when the recipient is offline; never for online recipients</t>
+          <t>Send a REAL photo in chat: upload to R2, deliver, recipient downloads identical bytes</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>send with peer offline / online</t>
+          <t>chat presign + PUT + WS image</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>offline recipient -&gt; 1 push with sender name and match id; online recipient -&gt; 0 pushes</t>
+          <t>chat presign 200, R2 PUT 200, WS image message delivered with image_url, download hash equals upload, history shows message_type=image</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>offline push count: 1; push mentions sender name: 'QAc4F'; online push count: 0</t>
+          <t>R2 PUT: 200; type: 'image'; image_url present: True; download: 200; bytes identical: '58b84aacfa05662b2a0fb64af8063aa89005c3829a875a0007aa53995d0c6951'; history has image message: True</t>
         </is>
       </c>
       <c r="H78" s="11" t="inlineStr">
@@ -5808,13 +5804,13 @@
       </c>
       <c r="L78" s="10" t="inlineStr"/>
       <c r="M78" s="10" t="n">
-        <v>14.03</v>
+        <v>14.61</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>CHAT-005</t>
+          <t>CHAT-003</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
@@ -5824,27 +5820,27 @@
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Real-time translation</t>
+          <t>Input handling</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>Cross-language chat (ko sender -&gt; en recipient) is translated by the real Google Translate API</t>
+          <t>Empty, whitespace-only, very long, emoji/RTL/HTML messages</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>REAL Google Cloud Translation call</t>
+          <t>send edge-case messages</t>
         </is>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>delivered message carries translated_content in English and original_language ko; history keeps both</t>
+          <t>empty and whitespace ignored (not stored); 5000-char message stored intact; emoji/RTL/HTML stored verbatim (clients escape); connection stays alive</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
         <is>
-          <t>message received: True; original_language: 'ko'; translated_language: 'en'; translation non-empty and different: 'Hello, nice to meet you.'</t>
+          <t>long message delivered intact: '가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가가</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
@@ -5863,19 +5859,15 @@
       <c r="K79" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="L79" s="10" t="inlineStr">
-        <is>
-          <t>translated -&gt; 'Hello, nice to meet you.'</t>
-        </is>
-      </c>
+      <c r="L79" s="10" t="inlineStr"/>
       <c r="M79" s="10" t="n">
-        <v>13.58</v>
+        <v>17.48</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>CHAT-006</t>
+          <t>CHAT-004</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
@@ -5885,27 +5877,27 @@
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Robustness</t>
+          <t>Push routing</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Malformed WebSocket frames do not take the server down</t>
+          <t>Push only when the recipient is offline; never for online recipients</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>send garbage frames then use the API</t>
+          <t>send with peer offline / online</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>non-JSON text, JSON array, unknown type, missing match_id, bad uuid: server keeps serving other requests; valid users unaffected</t>
+          <t>offline recipient -&gt; 1 push with sender name and match id; online recipient -&gt; 0 pushes</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>API healthy: 200; valid message after garbage stored: True; non-JSON frame tolerated (connection may close, server must live): True; API still healthy: 200</t>
+          <t>offline push count: 1; push mentions sender name: 'QAc4F'; online push count: 0</t>
         </is>
       </c>
       <c r="H80" s="11" t="inlineStr">
@@ -5926,13 +5918,13 @@
       </c>
       <c r="L80" s="10" t="inlineStr"/>
       <c r="M80" s="10" t="n">
-        <v>13.72</v>
+        <v>14.03</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>CHAT-007</t>
+          <t>CHAT-005</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
@@ -5942,27 +5934,27 @@
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Spam / rate limiting</t>
+          <t>Real-time translation</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>Burst of 60 messages in a second</t>
+          <t>Cross-language chat (ko sender -&gt; en recipient) is translated by the real Google Translate API</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
-          <t>send 60 messages fast</t>
+          <t>REAL Google Cloud Translation call</t>
         </is>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>server either throttles (some rejected) or stores them all without crashing; documents whether per-user rate limiting exists</t>
+          <t>delivered message carries translated_content in English and original_language ko; history keeps both</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>no crash, count in 1..60: 4</t>
+          <t>message received: True; original_language: 'ko'; translated_language: 'en'; translation non-empty and different: 'Hello, nice to meet you.'</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
@@ -5983,17 +5975,17 @@
       </c>
       <c r="L81" s="10" t="inlineStr">
         <is>
-          <t>stored 4/60 -&gt; throttled</t>
+          <t>translated -&gt; 'Hello, nice to meet you.'</t>
         </is>
       </c>
       <c r="M81" s="10" t="n">
-        <v>17.73</v>
+        <v>13.58</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>CHAT-008</t>
+          <t>CHAT-006</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
@@ -6003,27 +5995,27 @@
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>History pagination</t>
+          <t>Robustness</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>limit and before parameters</t>
+          <t>Malformed WebSocket frames do not take the server down</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>seed 5 messages, page through</t>
+          <t>send garbage frames then use the API</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>limit=2 returns 2; before=&lt;timestamp&gt; returns older ones; limit 0/201 -&gt; 422</t>
+          <t>non-JSON text, JSON array, unknown type, missing match_id, bad uuid: server keeps serving other requests; valid users unaffected</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>limit 2: 2; before returns strictly older: 1; limit 0: 422; limit 201: 422</t>
+          <t>API healthy: 200; valid message after garbage stored: True; non-JSON frame tolerated (connection may close, server must live): True; API still healthy: 200</t>
         </is>
       </c>
       <c r="H82" s="11" t="inlineStr">
@@ -6044,13 +6036,13 @@
       </c>
       <c r="L82" s="10" t="inlineStr"/>
       <c r="M82" s="10" t="n">
-        <v>16.39</v>
+        <v>13.72</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>CALL-001</t>
+          <t>CHAT-007</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
@@ -6060,27 +6052,27 @@
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Video call signaling</t>
+          <t>Spam / rate limiting</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>Offer / answer / ICE / hang-up relay; offline callee ends immediately; outsider ignored; ICE server list served</t>
+          <t>Burst of 60 messages in a second</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>WS signaling between matched pair</t>
+          <t>send 60 messages fast</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>frames relayed exactly; offline callee gets call_end peer_offline; outsider's offer creates nothing; /calls/ice-servers returns STUN urls</t>
+          <t>server either throttles (some rejected) or stores them all without crashing; documents whether per-user rate limiting exists</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>offline callee: 'peer_offline'; offer relayed: ('call_offer', 'offer-sdp', '774eb50a-bd91-42c4-9ca6-5a9824612732'); answer relayed: 'answer-sdp'; ice relayed: 'cand'; end relayed: 'hangup'; ice-servers status: 200; has stun url: True</t>
+          <t>no crash, count in 1..60: 4</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
@@ -6099,45 +6091,49 @@
       <c r="K83" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="L83" s="10" t="inlineStr"/>
+      <c r="L83" s="10" t="inlineStr">
+        <is>
+          <t>stored 4/60 -&gt; throttled</t>
+        </is>
+      </c>
       <c r="M83" s="10" t="n">
-        <v>20.11</v>
+        <v>17.73</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>BLIND-001</t>
+          <t>CHAT-008</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>블라인드 채팅·AI매칭</t>
+          <t>채팅·통화</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Queue &amp; pairing</t>
+          <t>History pagination</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>Two compatible people are paired; identities stay masked; bio visible; shared categories shown</t>
+          <t>limit and before parameters</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>queue A, queue B</t>
+          <t>seed 5 messages, page through</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>first joiner 'waiting', second 'matched'; A's status becomes matched with same id; names masked to 'X***' with no photo; blind flags set; matched push to the waiting user</t>
+          <t>limit=2 returns 2; before=&lt;timestamp&gt; returns older ones; limit 0/201 -&gt; 422</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>A waiting: 'waiting'; B matched: 'matched'; A status matched: ('matched', '6194ba0a-b8a3-4205-b705-b010edad617f'); is_blind: True; masked name: 'Q***'; no photo: None; shared categories: ['food']; matched push to A: True</t>
+          <t>limit 2: 2; before returns strictly older: 1; limit 0: 422; limit 201: 422</t>
         </is>
       </c>
       <c r="H84" s="11" t="inlineStr">
@@ -6158,43 +6154,43 @@
       </c>
       <c r="L84" s="10" t="inlineStr"/>
       <c r="M84" s="10" t="n">
-        <v>12.9</v>
+        <v>16.39</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>BLIND-002</t>
+          <t>CALL-001</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>블라인드 채팅·AI매칭</t>
+          <t>채팅·통화</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Messaging</t>
+          <t>Video call signaling</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>Blind chat opens immediately in both directions (no first-message gate) with realtime delivery</t>
+          <t>Offer / answer / ICE / hang-up relay; offline callee ends immediately; outsider ignored; ICE server list served</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>WS chat inside a blind match</t>
+          <t>WS signaling between matched pair</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>man's message delivered right away; woman's too; history has both</t>
+          <t>frames relayed exactly; offline callee gets call_end peer_offline; outsider's offer creates nothing; /calls/ice-servers returns STUN urls</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>man first delivered: '익명 첫 마디'; woman delivered: '반가워요'; history count: 2</t>
+          <t>offline callee: 'peer_offline'; offer relayed: ('call_offer', 'offer-sdp', '774eb50a-bd91-42c4-9ca6-5a9824612732'); answer relayed: 'answer-sdp'; ice relayed: 'cand'; end relayed: 'hangup'; ice-servers status: 200; has stun url: True</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
@@ -6215,13 +6211,13 @@
       </c>
       <c r="L85" s="10" t="inlineStr"/>
       <c r="M85" s="10" t="n">
-        <v>3.09</v>
+        <v>20.11</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>BLIND-003</t>
+          <t>BLIND-001</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
@@ -6231,27 +6227,27 @@
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Identity reveal</t>
+          <t>Queue &amp; pairing</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>Only the eligible side can request a reveal; the other accepts; both unmasked; self-accept refused</t>
+          <t>Two compatible people are paired; identities stay masked; bio visible; shared categories shown</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>reveal request/accept flow</t>
+          <t>queue A, queue B</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>woman (eligible in mixed pair) requests -&gt; man sees incoming request; man cannot request; woman cannot self-accept; man accepts -&gt; real names+photos on both sides; reveal pushes recorded</t>
+          <t>first joiner 'waiting', second 'matched'; A's status becomes matched with same id; names masked to 'X***' with no photo; blind flags set; matched push to the waiting user</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>man can_request_reveal: False; woman can_request_reveal: True; man's request refused: True; woman request: 200; reveal_requested_by_me: True; request push to man: True; man sees incoming request: True; self-accept refused: 400; man accepts: 200; man sees woman's real name: 'QAb1F'; woman sees man's real name: 'QAb1M'; photos visible after reveal: True; blind_revealed: True</t>
+          <t>A waiting: 'waiting'; B matched: 'matched'; A status matched: ('matched', '6194ba0a-b8a3-4205-b705-b010edad617f'); is_blind: True; masked name: 'Q***'; no photo: None; shared categories: ['food']; matched push to A: True</t>
         </is>
       </c>
       <c r="H86" s="11" t="inlineStr">
@@ -6272,13 +6268,13 @@
       </c>
       <c r="L86" s="10" t="inlineStr"/>
       <c r="M86" s="10" t="n">
-        <v>9.539999999999999</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>BLIND-004</t>
+          <t>BLIND-002</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
@@ -6288,27 +6284,27 @@
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Messaging</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>Post-chat rating: rating 1-5, tags, 'other' comment rule, upsert, outsider refused</t>
+          <t>Blind chat opens immediately in both directions (no first-message gate) with realtime delivery</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>POST /matches/{id}/blind-feedback variants</t>
+          <t>WS chat inside a blind match</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>rating 5 + tags ok; rating 0/6 -&gt; 422; unknown tag 422; comment without 'other' 422; resubmit updates (no duplicate); outsider 403/404; non-blind match refused</t>
+          <t>man's message delivered right away; woman's too; history has both</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>ok: 200; rating 0: 422; rating 6: 422; unknown tag: 422; comment without other: 422; upsert: 200; stored rating updated: 2; outsider refused: True; non-blind match refused: 400</t>
+          <t>man first delivered: '익명 첫 마디'; woman delivered: '반가워요'; history count: 2</t>
         </is>
       </c>
       <c r="H87" s="11" t="inlineStr">
@@ -6329,13 +6325,13 @@
       </c>
       <c r="L87" s="10" t="inlineStr"/>
       <c r="M87" s="10" t="n">
-        <v>20.63</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>BLIND-005</t>
+          <t>BLIND-003</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
@@ -6345,27 +6341,27 @@
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Matching rules</t>
+          <t>Identity reveal</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>Session gender choice beats profile; age filter honoured; wrong gender never pairs</t>
+          <t>Only the eligible side can request a reveal; the other accepts; both unmasked; self-accept refused</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>queue with overrides</t>
+          <t>reveal request/accept flow</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>profile says seeks female, session picks 'male' -&gt; pairs only with a man; a woman waiting is NOT paired; age mismatch stays waiting</t>
+          <t>woman (eligible in mixed pair) requests -&gt; man sees incoming request; man cannot request; woman cannot self-accept; man accepts -&gt; real names+photos on both sides; reveal pushes recorded</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>woman waits: 'waiting'; male override does NOT pair with the woman: 'waiting'; male pairs with male seeker: 'matched'; age mismatch stays waiting: 'waiting'</t>
+          <t>man can_request_reveal: False; woman can_request_reveal: True; man's request refused: True; woman request: 200; reveal_requested_by_me: True; request push to man: True; man sees incoming request: True; self-accept refused: 400; man accepts: 200; man sees woman's real name: 'QAb1F'; woman sees man's real name: 'QAb1M'; photos visible after reveal: True; blind_revealed: True</t>
         </is>
       </c>
       <c r="H88" s="11" t="inlineStr">
@@ -6386,13 +6382,13 @@
       </c>
       <c r="L88" s="10" t="inlineStr"/>
       <c r="M88" s="10" t="n">
-        <v>28.03</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>BLIND-006</t>
+          <t>BLIND-004</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
@@ -6402,27 +6398,27 @@
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Queue lifecycle</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>Cancel, re-join, repeated join, validation</t>
+          <t>Post-chat rating: rating 1-5, tags, 'other' comment rule, upsert, outsider refused</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr">
         <is>
-          <t>queue state machine</t>
+          <t>POST /matches/{id}/blind-feedback variants</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>DELETE -&gt; idle; second join after cancel waiting; repeated join idempotent; empty categories 422; 11 categories 422</t>
+          <t>rating 5 + tags ok; rating 0/6 -&gt; 422; unknown tag 422; comment without 'other' 422; resubmit updates (no duplicate); outsider 403/404; non-blind match refused</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>first join: 'waiting'; repeat join: 'waiting'; cancel: 204; status idle: 'idle'; rejoin: 'waiting'; empty categories: 422; 11 categories: 422</t>
+          <t>ok: 200; rating 0: 422; rating 6: 422; unknown tag: 422; comment without other: 422; upsert: 200; stored rating updated: 2; outsider refused: True; non-blind match refused: 400</t>
         </is>
       </c>
       <c r="H89" s="11" t="inlineStr">
@@ -6443,13 +6439,13 @@
       </c>
       <c r="L89" s="10" t="inlineStr"/>
       <c r="M89" s="10" t="n">
-        <v>9.49</v>
+        <v>20.63</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>BLIND-007</t>
+          <t>BLIND-005</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
@@ -6459,27 +6455,27 @@
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Matching rules</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>Blocked pairs are never paired; queue entry older than 15 min is ignored</t>
+          <t>Session gender choice beats profile; age filter honoured; wrong gender never pairs</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>block + backdate</t>
+          <t>queue with overrides</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>blocker + blocked both queue -&gt; stay waiting; stale (16 min) waiting entry not matched</t>
+          <t>profile says seeks female, session picks 'male' -&gt; pairs only with a man; a woman waiting is NOT paired; age mismatch stays waiting</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>blocked pair stays waiting: 'waiting'; stale entry ignored: 'waiting'</t>
+          <t>woman waits: 'waiting'; male override does NOT pair with the woman: 'waiting'; male pairs with male seeker: 'matched'; age mismatch stays waiting: 'waiting'</t>
         </is>
       </c>
       <c r="H90" s="11" t="inlineStr">
@@ -6500,13 +6496,13 @@
       </c>
       <c r="L90" s="10" t="inlineStr"/>
       <c r="M90" s="10" t="n">
-        <v>23.78</v>
+        <v>28.03</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>BLIND-008</t>
+          <t>BLIND-006</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
@@ -6516,27 +6512,27 @@
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Daily limit &amp; monetization</t>
+          <t>Queue lifecycle</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>5 free matches/day, ad bonus +1 once, then blocked; membership = unlimited</t>
+          <t>Cancel, re-join, repeated join, validation</t>
         </is>
       </c>
       <c r="E91" s="10" t="inlineStr">
         <is>
-          <t>6-7 real pairings for one viewer</t>
+          <t>queue state machine</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>limit shows 5; after 5 matches the 6th join 429; ad bonus -&gt; limit 6 (only once per day); 7th blocked; premium bypasses; bonus_available flips</t>
+          <t>DELETE -&gt; idle; second join after cancel waiting; repeated join idempotent; empty categories 422; 11 categories 422</t>
         </is>
       </c>
       <c r="G91" s="10" t="inlineStr">
         <is>
-          <t>limit: (5, 5, True); remaining after 5: 0; 6th blocked: 429; ad bonus: 200; limit after bonus: (6, 1, False); bonus claimed again: 6; 6th allowed after bonus: 'matched'; 7th blocked: 429; membership unlimited: 'matched'</t>
+          <t>first join: 'waiting'; repeat join: 'waiting'; cancel: 204; status idle: 'idle'; rejoin: 'waiting'; empty categories: 422; 11 categories: 422</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
@@ -6557,13 +6553,13 @@
       </c>
       <c r="L91" s="10" t="inlineStr"/>
       <c r="M91" s="10" t="n">
-        <v>57.58</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>BLIND-009</t>
+          <t>BLIND-007</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
@@ -6573,27 +6569,27 @@
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>AI match</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>AI match: needs a credit (402); with a credit finds the best waiting candidate and consumes exactly 1 credit; no candidates -&gt; credit untouched</t>
+          <t>Blocked pairs are never paired; queue entry older than 15 min is ignored</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>/blind-chat/ai-match with 0 and 2 credits</t>
+          <t>block + backdate</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>no credit 402; not found when nobody waits and credit unchanged; found with two waiting candidates, credit 2-&gt;1, match is blind. (The Claude re-rank layer is not exercised here: ANTHROPIC_API_KEY exists only in Railway, so this run covers the deterministic scoring + fallback path.)</t>
+          <t>blocker + blocked both queue -&gt; stay waiting; stale (16 min) waiting entry not matched</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>no credit: 402; nobody waiting -&gt; found False: False; credit untouched: 2; status: 200; found: True; credit consumed: 1; result is a blind match: True; picked one of the waiting candidates: True</t>
+          <t>blocked pair stays waiting: 'waiting'; stale entry ignored: 'waiting'</t>
         </is>
       </c>
       <c r="H92" s="11" t="inlineStr">
@@ -6614,13 +6610,13 @@
       </c>
       <c r="L92" s="10" t="inlineStr"/>
       <c r="M92" s="10" t="n">
-        <v>20.23</v>
+        <v>23.78</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>BLIND-010</t>
+          <t>BLIND-008</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
@@ -6630,27 +6626,27 @@
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Reporting inside blind chat</t>
+          <t>Daily limit &amp; monetization</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>Reporting an anonymous partner works and admin can read the conversation</t>
+          <t>5 free matches/day, ad bonus +1 once, then blocked; membership = unlimited</t>
         </is>
       </c>
       <c r="E93" s="10" t="inlineStr">
         <is>
-          <t>blind chat -&gt; report -&gt; admin</t>
+          <t>6-7 real pairings for one viewer</t>
         </is>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>report 204; admin conversation endpoint returns the blind chat messages</t>
+          <t>limit shows 5; after 5 matches the 6th join 429; ad bonus -&gt; limit 6 (only once per day); 7th blocked; premium bypasses; bonus_available flips</t>
         </is>
       </c>
       <c r="G93" s="10" t="inlineStr">
         <is>
-          <t>report: 204; admin sees blind conversation: ['inappropriate msg']</t>
+          <t>limit: (5, 5, True); remaining after 5: 0; 6th blocked: 429; ad bonus: 200; limit after bonus: (6, 1, False); bonus claimed again: 6; 6th allowed after bonus: 'matched'; 7th blocked: 429; membership unlimited: 'matched'</t>
         </is>
       </c>
       <c r="H93" s="11" t="inlineStr">
@@ -6671,43 +6667,43 @@
       </c>
       <c r="L93" s="10" t="inlineStr"/>
       <c r="M93" s="10" t="n">
-        <v>14.83</v>
+        <v>57.58</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>MOM-001</t>
+          <t>BLIND-009</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>모먼트</t>
+          <t>블라인드 채팅·AI매칭</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Lately (요즘 나)</t>
+          <t>AI match</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>Post a moment with a REAL photo; caption limit; rolling 6; delete; other user's delete refused</t>
+          <t>AI match: needs a credit (402); with a credit finds the best waiting candidate and consumes exactly 1 credit; no candidates -&gt; credit untouched</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>moment presign+PUT+create</t>
+          <t>/blind-chat/ai-match with 0 and 2 credits</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>created with image_url that downloads; caption 281 -&gt; 422; posting 8 keeps newest 6; delete own 204; delete another's 404; moments show up on the profile and in Discover</t>
+          <t>no credit 402; not found when nobody waits and credit unchanged; found with two waiting candidates, credit 2-&gt;1, match is blind. (The Claude re-rank layer is not exercised here: ANTHROPIC_API_KEY exists only in Railway, so this run covers the deterministic scoring + fallback path.)</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>PUT: 200; create: 201; image downloads: 200; caption 281: 422; shown on my profile: True; shown in Discover card: True; rolling limit: 6; newest first: 'm6'; other user delete: 404; own delete: 204; after delete: 5</t>
+          <t>no credit: 402; nobody waiting -&gt; found False: False; credit untouched: 2; status: 200; found: True; credit consumed: 1; result is a blind match: True; picked one of the waiting candidates: True</t>
         </is>
       </c>
       <c r="H94" s="11" t="inlineStr">
@@ -6728,43 +6724,43 @@
       </c>
       <c r="L94" s="10" t="inlineStr"/>
       <c r="M94" s="10" t="n">
-        <v>23.01</v>
+        <v>20.23</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>CS-001</t>
+          <t>BLIND-010</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>커플 스토리</t>
+          <t>블라인드 채팅·AI매칭</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>Community feed</t>
+          <t>Reporting inside blind chat</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>Story needs partner consent: pending -&gt; partner confirms -&gt; appears in the feed; author cannot self-confirm; one story per match</t>
+          <t>Reporting an anonymous partner works and admin can read the conversation</t>
         </is>
       </c>
       <c r="E95" s="10" t="inlineStr">
         <is>
-          <t>couple story lifecycle with a real story photo</t>
+          <t>blind chat -&gt; report -&gt; admin</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>create 201 pending + request push to partner; hidden from feed; author confirm 404; partner confirm -&gt; published + push to author; visible to others in feed; second story 409; outsider create 404</t>
+          <t>report 204; admin conversation endpoint returns the blind chat messages</t>
         </is>
       </c>
       <c r="G95" s="10" t="inlineStr">
         <is>
-          <t>photo PUT: 200; create: 201; status pending: 'pending'; request push to partner: True; hidden from feed while pending: True; author self-confirm refused: 404; outsider confirm refused: 404; partner confirm: 200; published: 'published'; published push to author: True; visible in feed to others: True; photo downloadable: True; second story same match: 409; outsider cannot create: 404; in author's mine list: True</t>
+          <t>report: 204; admin sees blind conversation: ['inappropriate msg']</t>
         </is>
       </c>
       <c r="H95" s="11" t="inlineStr">
@@ -6785,43 +6781,43 @@
       </c>
       <c r="L95" s="10" t="inlineStr"/>
       <c r="M95" s="10" t="n">
-        <v>22.91</v>
+        <v>14.83</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>CS-002</t>
+          <t>MOM-001</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>커플 스토리</t>
+          <t>모먼트</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>Decline &amp; report</t>
+          <t>Lately (요즘 나)</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>Partner can decline; 3 distinct reports auto-hide a published story; validation</t>
+          <t>Post a moment with a REAL photo; caption limit; rolling 6; delete; other user's delete refused</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>decline path and report threshold</t>
+          <t>moment presign+PUT+create</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>decline -&gt; declined and never in feed; declined story cannot be confirmed later; 3 reports hide the published story; empty text 422; 2001 chars 422</t>
+          <t>created with image_url that downloads; caption 281 -&gt; 422; posting 8 keeps newest 6; delete own 204; delete another's 404; moments show up on the profile and in Discover</t>
         </is>
       </c>
       <c r="G96" s="10" t="inlineStr">
         <is>
-          <t>decline: (200, 'declined'); confirm after decline: 404; never in feed: True; empty text: 422; 2001 chars: 422; report: 204; report: 204; report: 204; auto-hidden after 3 reports: True</t>
+          <t>PUT: 200; create: 201; image downloads: 200; caption 281: 422; shown on my profile: True; shown in Discover card: True; rolling limit: 6; newest first: 'm6'; other user delete: 404; own delete: 204; after delete: 5</t>
         </is>
       </c>
       <c r="H96" s="11" t="inlineStr">
@@ -6842,43 +6838,43 @@
       </c>
       <c r="L96" s="10" t="inlineStr"/>
       <c r="M96" s="10" t="n">
-        <v>34.21</v>
+        <v>23.01</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PAY-001</t>
+          <t>CS-001</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>결제</t>
+          <t>커플 스토리</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Shop catalog</t>
+          <t>Community feed</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>Product list: only listed products, correct kinds, prices in cents, no hidden classic products</t>
+          <t>Story needs partner consent: pending -&gt; partner confirms -&gt; appears in the feed; author cannot self-confirm; one story per match</t>
         </is>
       </c>
       <c r="E97" s="10" t="inlineStr">
         <is>
-          <t>GET /payments/products</t>
+          <t>couple story lifecycle with a real story photo</t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>ai_match packs, unlimited week/month, membership monthly/yearly present; superlike/boost packs hidden; prices positive ints</t>
+          <t>create 201 pending + request push to partner; hidden from feed; author confirm 404; partner confirm -&gt; published + push to author; visible to others in feed; second story 409; outsider create 404</t>
         </is>
       </c>
       <c r="G97" s="10" t="inlineStr">
         <is>
-          <t>expected products present: True; hidden classic products absent: True; prices positive ints: True; monthly price: 999</t>
+          <t>photo PUT: 200; create: 201; status pending: 'pending'; request push to partner: True; hidden from feed while pending: True; author self-confirm refused: 404; outsider confirm refused: 404; partner confirm: 200; published: 'published'; published push to author: True; visible in feed to others: True; photo downloadable: True; second story same match: 409; outsider cannot create: 404; in author's mine list: True</t>
         </is>
       </c>
       <c r="H97" s="11" t="inlineStr">
@@ -6899,43 +6895,43 @@
       </c>
       <c r="L97" s="10" t="inlineStr"/>
       <c r="M97" s="10" t="n">
-        <v>0.29</v>
+        <v>22.91</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>PAY-002</t>
+          <t>CS-002</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>결제</t>
+          <t>커플 스토리</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>Webhook</t>
+          <t>Decline &amp; report</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>Signed Stripe purchase grants credits exactly once; replay is a no-op; forged/missing signature rejected; unrelated events ignored</t>
+          <t>Partner can decline; 3 distinct reports auto-hide a published story; validation</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>locally-signed checkout.session.completed events</t>
+          <t>decline path and report threshold</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>ai_match_pack_5 -&gt; +5 credits + history row; replaying same event id -&gt; still 5; bad signature 400; no signature 400; other event types 204 with no effect; unknown product ignored</t>
+          <t>decline -&gt; declined and never in feed; declined story cannot be confirmed later; 3 reports hide the published story; empty text 422; 2001 chars 422</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>webhook: 204; credits granted: 5; replay no double grant: 5; history rows: 1; history product: 'ai_match_pack_5'; forged signature: 400; missing signature: 400; unrelated event: 204; unknown product ignored: 204; credits unchanged: 5</t>
+          <t>decline: (200, 'declined'); confirm after decline: 404; never in feed: True; empty text: 422; 2001 chars: 422; report: 204; report: 204; report: 204; auto-hidden after 3 reports: True</t>
         </is>
       </c>
       <c r="H98" s="11" t="inlineStr">
@@ -6956,13 +6952,13 @@
       </c>
       <c r="L98" s="10" t="inlineStr"/>
       <c r="M98" s="10" t="n">
-        <v>7.51</v>
+        <v>34.21</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PAY-003</t>
+          <t>PAY-001</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
@@ -6972,27 +6968,27 @@
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Membership</t>
+          <t>Shop catalog</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>Membership purchase -&gt; premium status everywhere; cancel keeps access until period end; yearly replaces monthly</t>
+          <t>Product list: only listed products, correct kinds, prices in cents, no hidden classic products</t>
         </is>
       </c>
       <c r="E99" s="10" t="inlineStr">
         <is>
-          <t>webhook membership_monthly then cancel</t>
+          <t>GET /payments/products</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>profile is_premium_member True, premium_until ~30d, billing monthly; unlimited swipes + blind matching; cancel -&gt; cancel_at_period_end True, premium_until kept; cancel with no membership refused</t>
+          <t>ai_match packs, unlimited week/month, membership monthly/yearly present; superlike/boost packs hidden; prices positive ints</t>
         </is>
       </c>
       <c r="G99" s="10" t="inlineStr">
         <is>
-          <t>is_premium_member: True; billing_cycle: 'monthly'; price: 999; premium_until about 30 days: 29; swipes unlimited: True; blind unlimited: True; cancel responds (Stripe sub id is fake -&gt; may 4xx/5xx from Stripe): 502; cancel without membership refused: True; yearly replaces monthly: ('yearly', 9999)</t>
+          <t>expected products present: True; hidden classic products absent: True; prices positive ints: True; monthly price: 999</t>
         </is>
       </c>
       <c r="H99" s="11" t="inlineStr">
@@ -7013,13 +7009,13 @@
       </c>
       <c r="L99" s="10" t="inlineStr"/>
       <c r="M99" s="10" t="n">
-        <v>13.21</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>PAY-004</t>
+          <t>PAY-002</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
@@ -7029,27 +7025,27 @@
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>Top-ups</t>
+          <t>Webhook</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>Unlimited-matching week/month stack on remaining time; purchase history localised in the user's language</t>
+          <t>Signed Stripe purchase grants credits exactly once; replay is a no-op; forged/missing signature rejected; unrelated events ignored</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>webhook x2, history with ko</t>
+          <t>locally-signed checkout.session.completed events</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>two week packs -&gt; ~14 days; history names in Korean when preferred_language=ko; only own rows</t>
+          <t>ai_match_pack_5 -&gt; +5 credits + history row; replaying same event id -&gt; still 5; bad signature 400; no signature 400; other event types 204 with no effect; unknown product ignored</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>stacked ~14 days: 14.0; blind unlimited: True; history name localised (ko): ['무제한 매칭 1주일']; history name localised (ja): ['無制限マッチング — 1週間']; history name localised (es): ['Matching ilimitado — 1 semana']; history name localised (zh): ['无限匹配 — 1周']; history name localised (en): ['Unlimited Matching — 1 week']; 5 languages give distinct names: {'ko': '무제한 매칭 1주일', 'ja': '無制限マッチング — 1週間', 'es': 'Matching ilimitado — 1 semana', 'zh': '无限匹配 — 1周', 'en': 'Unlimited Matching — 1 week'}</t>
+          <t>webhook: 204; credits granted: 5; replay no double grant: 5; history rows: 1; history product: 'ai_match_pack_5'; forged signature: 400; missing signature: 400; unrelated event: 204; unknown product ignored: 204; credits unchanged: 5</t>
         </is>
       </c>
       <c r="H100" s="11" t="inlineStr">
@@ -7070,13 +7066,13 @@
       </c>
       <c r="L100" s="10" t="inlineStr"/>
       <c r="M100" s="10" t="n">
-        <v>11.6</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PAY-005</t>
+          <t>PAY-003</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
@@ -7086,27 +7082,27 @@
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Checkout</t>
+          <t>Membership</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>Checkout session creation (Stripe test/live key aware)</t>
+          <t>Membership purchase -&gt; premium status everywhere; cancel keeps access until period end; yearly replaces monthly</t>
         </is>
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>POST /payments/create-checkout-session</t>
+          <t>webhook membership_monthly then cancel</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>unknown product 400/404; valid product returns a checkout.stripe.com URL when a TEST key is configured; skipped (not created) with a live key</t>
+          <t>profile is_premium_member True, premium_until ~30d, billing monthly; unlimited swipes + blind matching; cancel -&gt; cancel_at_period_end True, premium_until kept; cancel with no membership refused</t>
         </is>
       </c>
       <c r="G101" s="10" t="inlineStr">
         <is>
-          <t>unknown product rejected: 400; live/unset key: real session intentionally not created: True</t>
+          <t>is_premium_member: True; billing_cycle: 'monthly'; price: 999; premium_until about 30 days: 29; swipes unlimited: True; blind unlimited: True; cancel responds (Stripe sub id is fake -&gt; may 4xx/5xx from Stripe): 502; cancel without membership refused: True; yearly replaces monthly: ('yearly', 9999)</t>
         </is>
       </c>
       <c r="H101" s="11" t="inlineStr">
@@ -7125,19 +7121,15 @@
       <c r="K101" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="L101" s="10" t="inlineStr">
-        <is>
-          <t>stripe key mode: live</t>
-        </is>
-      </c>
+      <c r="L101" s="10" t="inlineStr"/>
       <c r="M101" s="10" t="n">
-        <v>4.21</v>
+        <v>13.21</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>PAY-006</t>
+          <t>PAY-004</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -7147,27 +7139,27 @@
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Boost</t>
+          <t>Top-ups</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Boost activation consumes a credit, 30-minute window; no credit -&gt; 402</t>
+          <t>Unlimited-matching week/month stack on remaining time; purchase history localised in the user's language</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>activate boost</t>
+          <t>webhook x2, history with ko</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>no credit 402; with credit 200 and boost_active_until ~30 min ahead; credit consumed</t>
+          <t>two week packs -&gt; ~14 days; history names in Korean when preferred_language=ko; only own rows</t>
         </is>
       </c>
       <c r="G102" s="10" t="inlineStr">
         <is>
-          <t>no credit: 402; activate: 200; ~30 minutes: 30.0; credit consumed: 0</t>
+          <t>stacked ~14 days: 14.0; blind unlimited: True; history name localised (ko): ['무제한 매칭 1주일']; history name localised (ja): ['無制限マッチング — 1週間']; history name localised (es): ['Matching ilimitado — 1 semana']; history name localised (zh): ['无限匹配 — 1周']; history name localised (en): ['Unlimited Matching — 1 week']; 5 languages give distinct names: {'ko': '무제한 매칭 1주일', 'ja': '無制限マッチング — 1週間', 'es': 'Matching ilimitado — 1 semana', 'zh': '无限匹配 — 1周', 'en': 'Unlimited Matching — 1 week'}</t>
         </is>
       </c>
       <c r="H102" s="11" t="inlineStr">
@@ -7188,43 +7180,43 @@
       </c>
       <c r="L102" s="10" t="inlineStr"/>
       <c r="M102" s="10" t="n">
-        <v>6.06</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PUSH-001</t>
+          <t>PAY-005</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>푸시·기기</t>
+          <t>결제</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>Localised notifications</t>
+          <t>Checkout</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>Verification-result push text exists in all 5 languages and differs per language</t>
+          <t>Checkout session creation (Stripe test/live key aware)</t>
         </is>
       </c>
       <c r="E103" s="10" t="inlineStr">
         <is>
-          <t>admin approves for users in each language</t>
+          <t>POST /payments/create-checkout-session</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>approved push title recorded for ko/en/es/zh/ja - 5 non-empty distinct titles</t>
+          <t>unknown product 400/404; valid product returns a checkout.stripe.com URL when a TEST key is configured; skipped (not created) with a live key</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
         <is>
-          <t>all 5 pushes sent: {'ko': '인증 완료! ✅', 'en': "You're verified! ✅", 'es': '¡Estás verificado! ✅', 'zh': '认证成功！✅', 'ja': '認証完了！✅'}; 5 distinct titles: 5</t>
+          <t>unknown product rejected: 400; live/unset key: real session intentionally not created: True</t>
         </is>
       </c>
       <c r="H103" s="11" t="inlineStr">
@@ -7237,55 +7229,55 @@
       </c>
       <c r="J103" s="10" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K103" s="10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L103" s="10" t="inlineStr">
         <is>
-          <t>{"ko": "인증 완료! ✅", "en": "You're verified! ✅", "es": "¡Estás verificado! ✅", "zh": "认证成功！✅", "ja": "認証完了！✅"}</t>
+          <t>stripe key mode: live</t>
         </is>
       </c>
       <c r="M103" s="10" t="n">
-        <v>44.05</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>DEV-001</t>
+          <t>PAY-006</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>푸시·기기</t>
+          <t>결제</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Device tokens</t>
+          <t>Boost</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>Register/re-register FCM token; validation; one user many devices</t>
+          <t>Boost activation consumes a credit, 30-minute window; no credit -&gt; 402</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>POST /devices/register</t>
+          <t>activate boost</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>204 for valid; re-register upsert 204; empty token 422; auth required</t>
+          <t>no credit 402; with credit 200 and boost_active_until ~30 min ahead; credit consumed</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>register: 204; re-register: 204; second device: 204; empty token rejected: True; auth required: True</t>
+          <t>no credit: 402; activate: 200; ~30 minutes: 30.0; credit consumed: 0</t>
         </is>
       </c>
       <c r="H104" s="11" t="inlineStr">
@@ -7306,43 +7298,43 @@
       </c>
       <c r="L104" s="10" t="inlineStr"/>
       <c r="M104" s="10" t="n">
-        <v>5.78</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>ACC-001</t>
+          <t>PUSH-001</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>계정</t>
+          <t>푸시·기기</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Account deletion</t>
+          <t>Localised notifications</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>Delete account: everything of the user is gone and the peer's match list is clean; phone can sign up again as NEW</t>
+          <t>Verification-result push text exists in all 5 languages and differs per language</t>
         </is>
       </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>delete a matched phone user, verify effects</t>
+          <t>admin approves for users in each language</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>204; token no longer works; profile gone from peer's deck and matches; same phone signs up as new user; old data not resurrected</t>
+          <t>approved push title recorded for ko/en/es/zh/ja - 5 non-empty distinct titles</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
         <is>
-          <t>match exists: True; delete: 204; token dead: True; match gone for peer: True; gone from peer's deck: True; re-signup is a new account: True; new id differs: True</t>
+          <t>all 5 pushes sent: {'ko': '인증 완료! ✅', 'en': "You're verified! ✅", 'es': '¡Estás verificado! ✅', 'zh': '认证成功！✅', 'ja': '認証完了！✅'}; 5 distinct titles: 5</t>
         </is>
       </c>
       <c r="H105" s="11" t="inlineStr">
@@ -7355,51 +7347,55 @@
       </c>
       <c r="J105" s="10" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K105" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="L105" s="10" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="L105" s="10" t="inlineStr">
+        <is>
+          <t>{"ko": "인증 완료! ✅", "en": "You're verified! ✅", "es": "¡Estás verificado! ✅", "zh": "认证成功！✅", "ja": "認証完了！✅"}</t>
+        </is>
+      </c>
       <c r="M105" s="10" t="n">
-        <v>16.37</v>
+        <v>44.05</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>SEC-001</t>
+          <t>DEV-001</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>푸시·기기</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Auth enforcement sweep</t>
+          <t>Device tokens</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Every non-public API route rejects anonymous callers</t>
+          <t>Register/re-register FCM token; validation; one user many devices</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>iterate the OpenAPI routes with no token</t>
+          <t>POST /devices/register</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>all routes except the public allowlist return 401/403/405/422-without-auth; none return 2xx or 5xx anonymously</t>
+          <t>204 for valid; re-register upsert 204; empty token 422; auth required</t>
         </is>
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>routes that answered 2xx/5xx anonymously: []</t>
+          <t>register: 204; re-register: 204; second device: 204; empty token rejected: True; auth required: True</t>
         </is>
       </c>
       <c r="H106" s="11" t="inlineStr">
@@ -7418,49 +7414,45 @@
       <c r="K106" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="L106" s="10" t="inlineStr">
-        <is>
-          <t>76 anonymous route calls</t>
-        </is>
-      </c>
+      <c r="L106" s="10" t="inlineStr"/>
       <c r="M106" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>SEC-002</t>
+          <t>ACC-001</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>계정</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Cross-user isolation</t>
+          <t>Account deletion</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>Users cannot read or change each other's data through any endpoint</t>
+          <t>Delete account: everything of the user is gone and the peer's match list is clean; phone can sign up again as NEW</t>
         </is>
       </c>
       <c r="E107" s="10" t="inlineStr">
         <is>
-          <t>IDOR attempts</t>
+          <t>delete a matched phone user, verify effects</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>user B cannot: delete A's photo, read A's face status, approve verifications, see A's purchase history rows, see A's moment list, confirm A's story</t>
+          <t>204; token no longer works; profile gone from peer's deck and matches; same phone signs up as new user; old data not resurrected</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
         <is>
-          <t>delete A's photo: 404; B's own face status independent: 'unsubmitted'; B is not admin: 403; B's history empty: []; B's balance untouched: 0</t>
+          <t>match exists: True; delete: 204; token dead: True; match gone for peer: True; gone from peer's deck: True; re-signup is a new account: True; new id differs: True</t>
         </is>
       </c>
       <c r="H107" s="11" t="inlineStr">
@@ -7481,13 +7473,13 @@
       </c>
       <c r="L107" s="10" t="inlineStr"/>
       <c r="M107" s="10" t="n">
-        <v>11.81</v>
+        <v>16.37</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>SEC-003</t>
+          <t>SEC-001</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
@@ -7497,27 +7489,27 @@
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>HTTP hardening</t>
+          <t>Auth enforcement sweep</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>Malformed bodies, wrong content types, oversize bodies, unsupported methods</t>
+          <t>Every non-public API route rejects anonymous callers</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>hostile requests</t>
+          <t>iterate the OpenAPI routes with no token</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>invalid JSON 422; text/plain body 422; 6 MB JSON body &lt;500; PATCH on a POST route 405; unknown path 404</t>
+          <t>all routes except the public allowlist return 401/403/405/422-without-auth; none return 2xx or 5xx anonymously</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
         <is>
-          <t>invalid JSON: 422; text/plain body: 422; 6MB body handled (&lt;500): 422; wrong method: 405; unknown path: 404</t>
+          <t>routes that answered 2xx/5xx anonymously: []</t>
         </is>
       </c>
       <c r="H108" s="11" t="inlineStr">
@@ -7536,15 +7528,19 @@
       <c r="K108" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="L108" s="10" t="inlineStr"/>
+      <c r="L108" s="10" t="inlineStr">
+        <is>
+          <t>76 anonymous route calls</t>
+        </is>
+      </c>
       <c r="M108" s="10" t="n">
-        <v>4.6</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>SEC-004</t>
+          <t>SEC-002</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
@@ -7554,27 +7550,27 @@
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>CORS</t>
+          <t>Cross-user isolation</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>Allowed web origins get CORS headers; unknown origins do not</t>
+          <t>Users cannot read or change each other's data through any endpoint</t>
         </is>
       </c>
       <c r="E109" s="10" t="inlineStr">
         <is>
-          <t>OPTIONS preflight</t>
+          <t>IDOR attempts</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>preflight from soodamate.com / localhost:8081 allowed; from evil.example not allowed</t>
+          <t>user B cannot: delete A's photo, read A's face status, approve verifications, see A's purchase history rows, see A's moment list, confirm A's story</t>
         </is>
       </c>
       <c r="G109" s="10" t="inlineStr">
         <is>
-          <t>soodamate.com allowed: 'https://www.soodamate.com'; mobile web allowed: 'http://localhost:8081'; evil origin not allowed: True</t>
+          <t>delete A's photo: 404; B's own face status independent: 'unsubmitted'; B is not admin: 403; B's history empty: []; B's balance untouched: 0</t>
         </is>
       </c>
       <c r="H109" s="11" t="inlineStr">
@@ -7595,13 +7591,13 @@
       </c>
       <c r="L109" s="10" t="inlineStr"/>
       <c r="M109" s="10" t="n">
-        <v>0</v>
+        <v>11.81</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>SEC-005</t>
+          <t>SEC-003</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
@@ -7611,27 +7607,27 @@
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>Information exposure</t>
+          <t>HTTP hardening</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>Public API docs / error bodies</t>
+          <t>Malformed bodies, wrong content types, oversize bodies, unsupported methods</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>GET /docs, /openapi.json, trigger a 404/422</t>
+          <t>hostile requests</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>informational: is /docs (Swagger) exposed publicly? Server errors never leak stack traces</t>
+          <t>invalid JSON 422; text/plain body 422; 6 MB JSON body &lt;500; PATCH on a POST route 405; unknown path 404</t>
         </is>
       </c>
       <c r="G110" s="10" t="inlineStr">
         <is>
-          <t>validation error has no traceback: True; informational recorded: True</t>
+          <t>invalid JSON: 422; text/plain body: 422; 6MB body handled (&lt;500): 422; wrong method: 405; unknown path: 404</t>
         </is>
       </c>
       <c r="H110" s="11" t="inlineStr">
@@ -7650,49 +7646,45 @@
       <c r="K110" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="L110" s="10" t="inlineStr">
-        <is>
-          <t>/docs -&gt; 200 (publicly exposed)</t>
-        </is>
-      </c>
+      <c r="L110" s="10" t="inlineStr"/>
       <c r="M110" s="10" t="n">
-        <v>0.01</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>I18N-001</t>
+          <t>SEC-004</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>다국어(i18n)</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Mobile app strings</t>
+          <t>CORS</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>All 5 language files contain exactly the same keys</t>
+          <t>Allowed web origins get CORS headers; unknown origins do not</t>
         </is>
       </c>
       <c r="E111" s="10" t="inlineStr">
         <is>
-          <t>flatten locales/*.json and diff key sets</t>
+          <t>OPTIONS preflight</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>0 missing / 0 extra keys in en, es, zh, ja relative to ko</t>
+          <t>preflight from soodamate.com / localhost:8081 allowed; from evil.example not allowed</t>
         </is>
       </c>
       <c r="G111" s="10" t="inlineStr">
         <is>
-          <t>en missing keys: []; en extra keys: []; es missing keys: []; es extra keys: []; zh missing keys: []; zh extra keys: []; ja missing keys: []; ja extra keys: []</t>
+          <t>soodamate.com allowed: 'https://www.soodamate.com'; mobile web allowed: 'http://localhost:8081'; evil origin not allowed: True</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
@@ -7705,15 +7697,13 @@
       </c>
       <c r="J111" s="10" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K111" s="10" t="n"/>
-      <c r="L111" s="10" t="inlineStr">
-        <is>
-          <t>818 keys in ko</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K111" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="L111" s="10" t="inlineStr"/>
       <c r="M111" s="10" t="n">
         <v>0</v>
       </c>
@@ -7721,37 +7711,37 @@
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>I18N-002</t>
+          <t>SEC-005</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>다국어(i18n)</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Mobile app strings</t>
+          <t>Information exposure</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>No empty, whitespace-only or placeholder ('TODO', '???') values in any language</t>
+          <t>Public API docs / error bodies</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>scan values</t>
+          <t>GET /docs, /openapi.json, trigger a 404/422</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>0 bad values per language</t>
+          <t>informational: is /docs (Swagger) exposed publicly? Server errors never leak stack traces</t>
         </is>
       </c>
       <c r="G112" s="10" t="inlineStr">
         <is>
-          <t>ko bad values: []; en bad values: []; es bad values: []; zh bad values: []; ja bad values: []</t>
+          <t>validation error has no traceback: True; informational recorded: True</t>
         </is>
       </c>
       <c r="H112" s="11" t="inlineStr">
@@ -7764,19 +7754,25 @@
       </c>
       <c r="J112" s="10" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K112" s="10" t="n"/>
-      <c r="L112" s="10" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K112" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="L112" s="10" t="inlineStr">
+        <is>
+          <t>/docs -&gt; 200 (publicly exposed)</t>
+        </is>
+      </c>
       <c r="M112" s="10" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>I18N-003</t>
+          <t>I18N-001</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
@@ -7791,22 +7787,22 @@
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>Interpolation variables ({{name}}) are identical across languages for every key</t>
+          <t>All 5 language files contain exactly the same keys</t>
         </is>
       </c>
       <c r="E113" s="10" t="inlineStr">
         <is>
-          <t>compare variable sets per key</t>
+          <t>flatten locales/*.json and diff key sets</t>
         </is>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>0 keys where a language drops or renames a variable (would print raw braces or blank)</t>
+          <t>0 missing / 0 extra keys in en, es, zh, ja relative to ko</t>
         </is>
       </c>
       <c r="G113" s="10" t="inlineStr">
         <is>
-          <t>mismatched variables: []</t>
+          <t>en missing keys: []; en extra keys: []; es missing keys: []; es extra keys: []; zh missing keys: []; zh extra keys: []; ja missing keys: []; ja extra keys: []</t>
         </is>
       </c>
       <c r="H113" s="11" t="inlineStr">
@@ -7823,7 +7819,11 @@
         </is>
       </c>
       <c r="K113" s="10" t="n"/>
-      <c r="L113" s="10" t="inlineStr"/>
+      <c r="L113" s="10" t="inlineStr">
+        <is>
+          <t>823 keys in ko</t>
+        </is>
+      </c>
       <c r="M113" s="10" t="n">
         <v>0</v>
       </c>
@@ -7831,7 +7831,7 @@
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>I18N-004</t>
+          <t>I18N-002</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
@@ -7846,22 +7846,22 @@
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>Every t('key') used in the source code exists in all 5 languages</t>
+          <t>No empty, whitespace-only or placeholder ('TODO', '???') values in any language</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>regex scan of src/**/*.ts(x) for static t() keys</t>
+          <t>scan values</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>0 missing keys (a missing key shows the raw key to users)</t>
+          <t>0 bad values per language</t>
         </is>
       </c>
       <c r="G114" s="10" t="inlineStr">
         <is>
-          <t>keys used in code but absent from ko.json: []</t>
+          <t>ko bad values: []; en bad values: []; es bad values: []; zh bad values: []; ja bad values: []</t>
         </is>
       </c>
       <c r="H114" s="11" t="inlineStr">
@@ -7878,19 +7878,15 @@
         </is>
       </c>
       <c r="K114" s="10" t="n"/>
-      <c r="L114" s="10" t="inlineStr">
-        <is>
-          <t>420 distinct static keys used</t>
-        </is>
-      </c>
+      <c r="L114" s="10" t="inlineStr"/>
       <c r="M114" s="10" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>I18N-005</t>
+          <t>I18N-003</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
@@ -7905,22 +7901,22 @@
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>Non-English files are actually translated (not left as English copies)</t>
+          <t>Interpolation variables ({{name}}) are identical across languages for every key</t>
         </is>
       </c>
       <c r="E115" s="10" t="inlineStr">
         <is>
-          <t>compare with en</t>
+          <t>compare variable sets per key</t>
         </is>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t>&lt;2% of long strings in es/zh/ja identical to English (brand names/acronyms excluded)</t>
+          <t>0 keys where a language drops or renames a variable (would print raw braces or blank)</t>
         </is>
       </c>
       <c r="G115" s="10" t="inlineStr">
         <is>
-          <t>es: 0/373 identical to English (0.0%): []; zh: 0/373 identical to English (0.0%): []; ja: 0/373 identical to English (0.0%): []; ko: 0/373 identical to English (0.0%): []</t>
+          <t>mismatched variables: []</t>
         </is>
       </c>
       <c r="H115" s="11" t="inlineStr">
@@ -7945,7 +7941,7 @@
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>I18N-006</t>
+          <t>I18N-004</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
@@ -7955,27 +7951,27 @@
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>Backend texts</t>
+          <t>Mobile app strings</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>Push-notification texts exist for all 5 languages for every notification type</t>
+          <t>Every t('key') used in the source code exists in all 5 languages</t>
         </is>
       </c>
       <c r="E116" s="10" t="inlineStr">
         <is>
-          <t>inspect app.services.push_i18n._STRINGS</t>
+          <t>regex scan of src/**/*.ts(x) for static t() keys</t>
         </is>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t>every key present in en also present and non-empty in ko/es/zh/ja (otherwise those users get English pushes)</t>
+          <t>0 missing keys (a missing key shows the raw key to users)</t>
         </is>
       </c>
       <c r="G116" s="10" t="inlineStr">
         <is>
-          <t>supported languages: ['en', 'es', 'ja', 'ko', 'zh']; ko missing keys: []; ko empty values: []; en missing keys: []; en empty values: []; es missing keys: []; es empty values: []; zh missing keys: []; zh empty values: []; ja missing keys: []; ja empty values: []</t>
+          <t>keys used in code but absent from ko.json: []</t>
         </is>
       </c>
       <c r="H116" s="11" t="inlineStr">
@@ -7994,17 +7990,17 @@
       <c r="K116" s="10" t="n"/>
       <c r="L116" s="10" t="inlineStr">
         <is>
-          <t>23 push strings</t>
+          <t>425 distinct static keys used</t>
         </is>
       </c>
       <c r="M116" s="10" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>I18N-007</t>
+          <t>I18N-005</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
@@ -8014,27 +8010,27 @@
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>Backend texts</t>
+          <t>Mobile app strings</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>Shop product names are localised for all 5 languages and differ per language</t>
+          <t>Non-English files are actually translated (not left as English copies)</t>
         </is>
       </c>
       <c r="E117" s="10" t="inlineStr">
         <is>
-          <t>payment_service._localized_product_name</t>
+          <t>compare with en</t>
         </is>
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t>every product has 5 non-empty names; membership name differs between ko/en/ja/zh/es</t>
+          <t>&lt;2% of long strings in es/zh/ja identical to English (brand names/acronyms excluded)</t>
         </is>
       </c>
       <c r="G117" s="10" t="inlineStr">
         <is>
-          <t>ai_match_pack_1 5 names: {'ko': 'AI 매칭권 1회', 'en': 'AI Match x1', 'es': '1 Match con IA', 'zh': 'AI匹配 x1', 'ja': 'AIマッチ ×1'}; ai_match_pack_5 5 names: {'ko': 'AI 매칭권 5회', 'en': 'AI Match x5', 'es': '5 Matches con IA', 'zh': 'AI匹配 x5', 'ja': 'AIマッチ ×5'}; unlimited_matching_week 5 names: {'ko': '무제한 매칭 1주일', 'en': 'Unlimited Matching — 1 week', 'es': 'Matching ilimitado — 1 semana', 'zh': '无限匹配 — 1周', 'ja': '無制限マッチング — 1週間'}; unlimited_matching_month 5 names: {'ko': '무제한 매칭 1개월', 'en': 'Unlimited Matching — 1 month', 'es': 'Matching ilimitado — 1 mes', 'zh': '无限匹配 — 1个月', 'ja': '無制限マッチング — 1ヶ月'}; membership_monthly 5 names: {'ko': '프리미엄 멤버십', 'en': 'Premium Membership', 'es': 'Membresía Premium', 'zh': '高级会员', 'ja': 'プレミアム会員'}; membership_yearly 5 names: {'ko': '프리미엄 멤버십', 'en': 'Premium Membership', 'es': 'Membresía Premium', 'zh': '高级会员', 'ja': 'プレミアム会員'}; superlike_pack_5 5 names: {'ko': '슈퍼좋아요 5개', 'en': 'Super Like x5', 'es': '5 Super Likes', 'zh': '超级喜欢 x5', 'ja': 'スーパーいいね ×5'}; superlike_pack_20 5 names: {'ko': '슈퍼좋아요 20개', 'en': 'Super Like x20', 'es': '20 Super Likes', 'zh': '超级喜欢 x20', 'ja': 'スーパーいいね ×20'}; boost_1 5 names: {'ko': '부스트 1회', 'en': 'Boost x1', 'es': '1 Boost', 'zh': '曝光加速 x1', 'ja': 'ブースト ×1'}; membership names distinct: 5</t>
+          <t>es: 0/377 identical to English (0.0%): []; zh: 0/377 identical to English (0.0%): []; ja: 0/377 identical to English (0.0%): []; ko: 0/377 identical to English (0.0%): []</t>
         </is>
       </c>
       <c r="H117" s="11" t="inlineStr">
@@ -8059,7 +8055,7 @@
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>I18N-101</t>
+          <t>I18N-006</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
@@ -8069,27 +8065,27 @@
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>Marketing site strings</t>
+          <t>Backend texts</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>Every web string exists in all 5 languages and is non-empty</t>
+          <t>Push-notification texts exist for all 5 languages for every notification type</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>load web/i18n.js translations</t>
+          <t>inspect app.services.push_i18n._STRINGS</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>0 keys with a missing/empty language</t>
+          <t>every key present in en also present and non-empty in ko/es/zh/ja (otherwise those users get English pushes)</t>
         </is>
       </c>
       <c r="G118" s="10" t="inlineStr">
         <is>
-          <t>ko missing/empty: []; en missing/empty: []; es missing/empty: []; zh missing/empty: []; ja missing/empty: []</t>
+          <t>supported languages: ['en', 'es', 'ja', 'ko', 'zh']; ko missing keys: []; ko empty values: []; en missing keys: []; en empty values: []; es missing keys: []; es empty values: []; zh missing keys: []; zh empty values: []; ja missing keys: []; ja empty values: []</t>
         </is>
       </c>
       <c r="H118" s="11" t="inlineStr">
@@ -8108,17 +8104,17 @@
       <c r="K118" s="10" t="n"/>
       <c r="L118" s="10" t="inlineStr">
         <is>
-          <t>220 keys</t>
+          <t>23 push strings</t>
         </is>
       </c>
       <c r="M118" s="10" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>I18N-102</t>
+          <t>I18N-007</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
@@ -8128,27 +8124,27 @@
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>Marketing site strings</t>
+          <t>Backend texts</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>Every data-i18n key used in the HTML pages has a translation</t>
+          <t>Shop product names are localised for all 5 languages and differ per language</t>
         </is>
       </c>
       <c r="E119" s="10" t="inlineStr">
         <is>
-          <t>scan web/*.html</t>
+          <t>payment_service._localized_product_name</t>
         </is>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>0 keys referenced in HTML but missing from i18n.js</t>
+          <t>every product has 5 non-empty names; membership name differs between ko/en/ja/zh/es</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
         <is>
-          <t>missing keys: []; unused translation keys (informational): 19</t>
+          <t>ai_match_pack_1 5 names: {'ko': 'AI 매칭권 1회', 'en': 'AI Match x1', 'es': '1 Match con IA', 'zh': 'AI匹配 x1', 'ja': 'AIマッチ ×1'}; ai_match_pack_5 5 names: {'ko': 'AI 매칭권 5회', 'en': 'AI Match x5', 'es': '5 Matches con IA', 'zh': 'AI匹配 x5', 'ja': 'AIマッチ ×5'}; unlimited_matching_week 5 names: {'ko': '무제한 매칭 1주일', 'en': 'Unlimited Matching — 1 week', 'es': 'Matching ilimitado — 1 semana', 'zh': '无限匹配 — 1周', 'ja': '無制限マッチング — 1週間'}; unlimited_matching_month 5 names: {'ko': '무제한 매칭 1개월', 'en': 'Unlimited Matching — 1 month', 'es': 'Matching ilimitado — 1 mes', 'zh': '无限匹配 — 1个月', 'ja': '無制限マッチング — 1ヶ月'}; membership_monthly 5 names: {'ko': '프리미엄 멤버십', 'en': 'Premium Membership', 'es': 'Membresía Premium', 'zh': '高级会员', 'ja': 'プレミアム会員'}; membership_yearly 5 names: {'ko': '프리미엄 멤버십', 'en': 'Premium Membership', 'es': 'Membresía Premium', 'zh': '高级会员', 'ja': 'プレミアム会員'}; superlike_pack_5 5 names: {'ko': '슈퍼좋아요 5개', 'en': 'Super Like x5', 'es': '5 Super Likes', 'zh': '超级喜欢 x5', 'ja': 'スーパーいいね ×5'}; superlike_pack_20 5 names: {'ko': '슈퍼좋아요 20개', 'en': 'Super Like x20', 'es': '20 Super Likes', 'zh': '超级喜欢 x20', 'ja': 'スーパーいいね ×20'}; boost_1 5 names: {'ko': '부스트 1회', 'en': 'Boost x1', 'es': '1 Boost', 'zh': '曝光加速 x1', 'ja': 'ブースト ×1'}; membership names distinct: 5</t>
         </is>
       </c>
       <c r="H119" s="11" t="inlineStr">
@@ -8165,11 +8161,7 @@
         </is>
       </c>
       <c r="K119" s="10" t="n"/>
-      <c r="L119" s="10" t="inlineStr">
-        <is>
-          <t>201 keys referenced by 8 pages</t>
-        </is>
-      </c>
+      <c r="L119" s="10" t="inlineStr"/>
       <c r="M119" s="10" t="n">
         <v>0</v>
       </c>
@@ -8177,7 +8169,7 @@
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>I18N-103</t>
+          <t>I18N-101</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
@@ -8192,22 +8184,22 @@
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>HTML markup inside translations is consistent across languages (&lt;br&gt;, &lt;span class=accent&gt;...)</t>
+          <t>Every web string exists in all 5 languages and is non-empty</t>
         </is>
       </c>
       <c r="E120" s="10" t="inlineStr">
         <is>
-          <t>compare tag multisets</t>
+          <t>load web/i18n.js translations</t>
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>same set of HTML tags in every language of each key</t>
+          <t>0 keys with a missing/empty language</t>
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr">
         <is>
-          <t>tag mismatches: []</t>
+          <t>ko missing/empty: []; en missing/empty: []; es missing/empty: []; zh missing/empty: []; ja missing/empty: []</t>
         </is>
       </c>
       <c r="H120" s="11" t="inlineStr">
@@ -8224,15 +8216,19 @@
         </is>
       </c>
       <c r="K120" s="10" t="n"/>
-      <c r="L120" s="10" t="inlineStr"/>
+      <c r="L120" s="10" t="inlineStr">
+        <is>
+          <t>220 keys</t>
+        </is>
+      </c>
       <c r="M120" s="10" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>I18N-104</t>
+          <t>I18N-102</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
@@ -8247,22 +8243,22 @@
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>Website default language is English and the choice persists</t>
+          <t>Every data-i18n key used in the HTML pages has a translation</t>
         </is>
       </c>
       <c r="E121" s="10" t="inlineStr">
         <is>
-          <t>inspect i18n.js</t>
+          <t>scan web/*.html</t>
         </is>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>currentLang() falls back to 'en'; 5 languages in the dropdown with flags</t>
+          <t>0 keys referenced in HTML but missing from i18n.js</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
         <is>
-          <t>falls back to en: 'const saved = localStorage.getItem("sooda_lang");\n  return saved &amp;&amp; SUPPORTED_LANGS.includes(saved) ? saved : "en";'; persists in localStorage: True; flags for all 5: True</t>
+          <t>missing keys: []; unused translation keys (informational): 19</t>
         </is>
       </c>
       <c r="H121" s="11" t="inlineStr">
@@ -8279,45 +8275,49 @@
         </is>
       </c>
       <c r="K121" s="10" t="n"/>
-      <c r="L121" s="10" t="inlineStr"/>
+      <c r="L121" s="10" t="inlineStr">
+        <is>
+          <t>201 keys referenced by 8 pages</t>
+        </is>
+      </c>
       <c r="M121" s="10" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>WEB-001</t>
+          <t>I18N-103</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>웹사이트</t>
+          <t>다국어(i18n)</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>Page integrity</t>
+          <t>Marketing site strings</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>Every website page loads (HTTP 200) with title, language attribute and mobile viewport</t>
+          <t>HTML markup inside translations is consistent across languages (&lt;br&gt;, &lt;span class=accent&gt;...)</t>
         </is>
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>serve web/ locally (Vercel clean-URL rules) and fetch each page</t>
+          <t>compare tag multisets</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>index, shop, shop-success, terms, privacy-policy, delete-account, child-safety, verify, admin all 200; each has &lt;title&gt;, &lt;html lang&gt;, viewport</t>
+          <t>same set of HTML tags in every language of each key</t>
         </is>
       </c>
       <c r="G122" s="10" t="inlineStr">
         <is>
-          <t>GET /: 200; / title: True; / html lang: True; / viewport: True; GET /shop: 200; /shop title: True; /shop html lang: True; /shop viewport: True; GET /shop-success: 200; /shop-success title: True; /shop-success html lang: True; /shop-success viewport: True; GET /terms: 200; /terms title: True; /terms html lang: True; /terms viewport: True; GET /privacy-policy: 200; /privacy-policy title: True; /privacy-policy html lang: True; /privacy-policy viewport: True; GET /delete-account: 200; /delete-account title: True; /delete-account html lang: True; /delete-account viewport: True; GET /child-safety: 200; /child-safety title: True; /child-safety html lang: True; /child-safety viewport: True; GET /verify: 200; /verify title: True; /verify html lang: True; /verify viewport: True; GET /admin/: 200; /admin/ title: True; /admin/ html lang: True; /admin/ viewport: True</t>
+          <t>tag mismatches: []</t>
         </is>
       </c>
       <c r="H122" s="11" t="inlineStr">
@@ -8336,43 +8336,43 @@
       <c r="K122" s="10" t="n"/>
       <c r="L122" s="10" t="inlineStr"/>
       <c r="M122" s="10" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>WEB-002</t>
+          <t>I18N-104</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>웹사이트</t>
+          <t>다국어(i18n)</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>Link integrity</t>
+          <t>Marketing site strings</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>All local links, images, scripts and stylesheets resolve (no 404s)</t>
+          <t>Website default language is English and the choice persists</t>
         </is>
       </c>
       <c r="E123" s="10" t="inlineStr">
         <is>
-          <t>crawl href/src of each page against the local server</t>
+          <t>inspect i18n.js</t>
         </is>
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t>0 broken local references across all pages</t>
+          <t>currentLang() falls back to 'en'; 5 languages in the dropdown with flags</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
         <is>
-          <t>broken references: []</t>
+          <t>falls back to en: 'const saved = localStorage.getItem("sooda_lang");\n  return saved &amp;&amp; SUPPORTED_LANGS.includes(saved) ? saved : "en";'; persists in localStorage: True; flags for all 5: True</t>
         </is>
       </c>
       <c r="H123" s="11" t="inlineStr">
@@ -8389,19 +8389,15 @@
         </is>
       </c>
       <c r="K123" s="10" t="n"/>
-      <c r="L123" s="10" t="inlineStr">
-        <is>
-          <t>83 local references checked</t>
-        </is>
-      </c>
+      <c r="L123" s="10" t="inlineStr"/>
       <c r="M123" s="10" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>WEB-003</t>
+          <t>WEB-001</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
@@ -8411,27 +8407,27 @@
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>Legal pages</t>
+          <t>Page integrity</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>Store-required pages exist and say the right things (privacy, terms, delete-account, child safety, 18+)</t>
+          <t>Every website page loads (HTTP 200) with title, language attribute and mobile viewport</t>
         </is>
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>text checks on translations</t>
+          <t>serve web/ locally (Vercel clean-URL rules) and fetch each page</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>privacy/terms/delete-account/child-safety pages have real content in all 5 languages; delete page lists photo/data deletion; child safety states 18+</t>
+          <t>index, shop, shop-success, terms, privacy-policy, delete-account, child-safety, verify, admin all 200; each has &lt;title&gt;, &lt;html lang&gt;, viewport</t>
         </is>
       </c>
       <c r="G124" s="10" t="inlineStr">
         <is>
-          <t>privacy: 27 strings: 27; terms: 37 strings: 37; deleteAccount: 16 strings: 16; childSafety: 14 strings: 14; child safety mentions 18: True; delete page mentions photos: True</t>
+          <t>GET /: 200; / title: True; / html lang: True; / viewport: True; GET /shop: 200; /shop title: True; /shop html lang: True; /shop viewport: True; GET /shop-success: 200; /shop-success title: True; /shop-success html lang: True; /shop-success viewport: True; GET /terms: 200; /terms title: True; /terms html lang: True; /terms viewport: True; GET /privacy-policy: 200; /privacy-policy title: True; /privacy-policy html lang: True; /privacy-policy viewport: True; GET /delete-account: 200; /delete-account title: True; /delete-account html lang: True; /delete-account viewport: True; GET /child-safety: 200; /child-safety title: True; /child-safety html lang: True; /child-safety viewport: True; GET /verify: 200; /verify title: True; /verify html lang: True; /verify viewport: True; GET /admin/: 200; /admin/ title: True; /admin/ html lang: True; /admin/ viewport: True</t>
         </is>
       </c>
       <c r="H124" s="11" t="inlineStr">
@@ -8450,13 +8446,13 @@
       <c r="K124" s="10" t="n"/>
       <c r="L124" s="10" t="inlineStr"/>
       <c r="M124" s="10" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>WEB-004</t>
+          <t>WEB-002</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
@@ -8466,27 +8462,27 @@
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>Shop</t>
+          <t>Link integrity</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>Shop page reads live prices from the API (no hard-coded prices) and product names render per language</t>
+          <t>All local links, images, scripts and stylesheets resolve (no 404s)</t>
         </is>
       </c>
       <c r="E125" s="10" t="inlineStr">
         <is>
-          <t>inspect shop.html</t>
+          <t>crawl href/src of each page against the local server</t>
         </is>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t>shop.html fetches /payments/products; no literal $ prices in markup</t>
+          <t>0 broken local references across all pages</t>
         </is>
       </c>
       <c r="G125" s="10" t="inlineStr">
         <is>
-          <t>fetches products from API: True; no hard-coded $ prices: True; checkout via API: True</t>
+          <t>broken references: []</t>
         </is>
       </c>
       <c r="H125" s="11" t="inlineStr">
@@ -8503,45 +8499,49 @@
         </is>
       </c>
       <c r="K125" s="10" t="n"/>
-      <c r="L125" s="10" t="inlineStr"/>
+      <c r="L125" s="10" t="inlineStr">
+        <is>
+          <t>83 local references checked</t>
+        </is>
+      </c>
       <c r="M125" s="10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>CLAIM-001</t>
+          <t>WEB-003</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>웹↔앱 일치</t>
+          <t>웹사이트</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>Claim audit</t>
+          <t>Legal pages</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>Sign-up / verification claims on the website match how the app really signs people up</t>
+          <t>Store-required pages exist and say the right things (privacy, terms, delete-account, child safety, 18+)</t>
         </is>
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>compare how.1.body with AuthStack</t>
+          <t>text checks on translations</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>website must not promise Apple/Google/email sign-up (app is phone-number-only)</t>
+          <t>privacy/terms/delete-account/child-safety pages have real content in all 5 languages; delete page lists photo/data deletion; child safety states 18+</t>
         </is>
       </c>
       <c r="G126" s="10" t="inlineStr">
         <is>
-          <t>app is phone-only: True; website does not promise Apple/Google/email sign-up: "enter your number, confirm the text-message code, and you're in — no passwords, no long forms."</t>
+          <t>privacy: 27 strings: 27; terms: 37 strings: 37; deleteAccount: 16 strings: 16; childSafety: 14 strings: 14; child safety mentions 18: True; delete page mentions photos: True</t>
         </is>
       </c>
       <c r="H126" s="11" t="inlineStr">
@@ -8554,12 +8554,10 @@
       </c>
       <c r="J126" s="10" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K126" s="10" t="n">
-        <v>50</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="10" t="n"/>
       <c r="L126" s="10" t="inlineStr"/>
       <c r="M126" s="10" t="n">
         <v>0</v>
@@ -8568,37 +8566,37 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>CLAIM-002</t>
+          <t>WEB-004</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>웹↔앱 일치</t>
+          <t>웹사이트</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Claim audit</t>
+          <t>Shop</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>'Face verification required to start Blind Chat' claim vs the app's actual rule</t>
+          <t>Shop page reads live prices from the API (no hard-coded prices) and product names render per language</t>
         </is>
       </c>
       <c r="E127" s="10" t="inlineStr">
         <is>
-          <t>grep blind_chat_service + web claims</t>
+          <t>inspect shop.html</t>
         </is>
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t>if the website says face verification is required, the backend must enforce it</t>
+          <t>shop.html fetches /payments/products; no literal $ prices in markup</t>
         </is>
       </c>
       <c r="G127" s="10" t="inlineStr">
         <is>
-          <t>website makes no such claim: True</t>
+          <t>fetches products from API: True; no hard-coded $ prices: True; checkout via API: True</t>
         </is>
       </c>
       <c r="H127" s="11" t="inlineStr">
@@ -8611,12 +8609,10 @@
       </c>
       <c r="J127" s="10" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K127" s="10" t="n">
-        <v>0</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="10" t="n"/>
       <c r="L127" s="10" t="inlineStr"/>
       <c r="M127" s="10" t="n">
         <v>0</v>
@@ -8625,7 +8621,7 @@
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>CLAIM-003</t>
+          <t>CLAIM-001</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
@@ -8640,22 +8636,22 @@
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>'Video call' claims vs the app's actual features</t>
+          <t>Sign-up / verification claims on the website match how the app really signs people up</t>
         </is>
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>grep mobile for WebRTC/call UI</t>
+          <t>compare how.1.body with AuthStack</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>website must not advertise video calling unless the app ships a call screen</t>
+          <t>website must not promise Apple/Google/email sign-up (app is phone-number-only)</t>
         </is>
       </c>
       <c r="G128" s="10" t="inlineStr">
         <is>
-          <t>website makes no video-call claim: True</t>
+          <t>app is phone-only: True; website does not promise Apple/Google/email sign-up: "enter your number, confirm the text-message code, and you're in — no passwords, no long forms."</t>
         </is>
       </c>
       <c r="H128" s="11" t="inlineStr">
@@ -8672,13 +8668,9 @@
         </is>
       </c>
       <c r="K128" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" s="10" t="inlineStr">
-        <is>
-          <t>claims: []</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="L128" s="10" t="inlineStr"/>
       <c r="M128" s="10" t="n">
         <v>0</v>
       </c>
@@ -8686,7 +8678,7 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>CLAIM-004</t>
+          <t>CLAIM-002</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
@@ -8701,22 +8693,22 @@
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>Every feature the website advertises exists in the app</t>
+          <t>'Face verification required to start Blind Chat' claim vs the app's actual rule</t>
         </is>
       </c>
       <c r="E129" s="10" t="inlineStr">
         <is>
-          <t>existence checks per advertised feature</t>
+          <t>grep blind_chat_service + web claims</t>
         </is>
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t>MBTI quiz, work/school verification, face verification, filters free, 5 languages, block/report all present in the app</t>
+          <t>if the website says face verification is required, the backend must enforce it</t>
         </is>
       </c>
       <c r="G129" s="10" t="inlineStr">
         <is>
-          <t>mbti_quiz: True; work_school_ui: True; face_verify_ui: True; 5 languages: 5</t>
+          <t>website makes no such claim: True</t>
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr">
@@ -8729,10 +8721,12 @@
       </c>
       <c r="J129" s="10" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K129" s="10" t="n"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K129" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L129" s="10" t="inlineStr"/>
       <c r="M129" s="10" t="n">
         <v>0</v>
@@ -8741,7 +8735,7 @@
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>CLAIM-005</t>
+          <t>CLAIM-003</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
@@ -8751,27 +8745,27 @@
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>Coverage audit</t>
+          <t>Claim audit</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>App strengths that are really usable today are showcased on the website</t>
+          <t>'Video call' claims vs the app's actual features</t>
         </is>
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>keyword coverage of the English marketing copy</t>
+          <t>grep mobile for WebRTC/call UI</t>
         </is>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>website mentions: instant translation, couple stories, icebreakers, AI match, free daily matches + membership, ID-checked badge</t>
+          <t>website must not advertise video calling unless the app ships a call screen</t>
         </is>
       </c>
       <c r="G130" s="10" t="inlineStr">
         <is>
-          <t>website mentions instant translation: True; website mentions couple stories: True; website mentions icebreakers: True; website mentions AI match: True; website mentions free daily matches: True; website mentions membership: True; website mentions ID-checked badge: True; website mentions block / report: True</t>
+          <t>website makes no video-call claim: True</t>
         </is>
       </c>
       <c r="H130" s="11" t="inlineStr">
@@ -8788,9 +8782,13 @@
         </is>
       </c>
       <c r="K130" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="L130" s="10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L130" s="10" t="inlineStr">
+        <is>
+          <t>claims: []</t>
+        </is>
+      </c>
       <c r="M130" s="10" t="n">
         <v>0</v>
       </c>
@@ -8798,7 +8796,7 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>CLAIM-006</t>
+          <t>CLAIM-004</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
@@ -8813,22 +8811,22 @@
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>Website does not advertise features that are hidden or absent in the current app</t>
+          <t>Every feature the website advertises exists in the app</t>
         </is>
       </c>
       <c r="E131" s="10" t="inlineStr">
         <is>
-          <t>grep English marketing copy for features removed from the app UI</t>
+          <t>existence checks per advertised feature</t>
         </is>
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
-          <t>no mention of travel mode, incognito, swipe/classic discovery, video calls, or sign-up via Apple/Google/email</t>
+          <t>MBTI quiz, work/school verification, face verification, filters free, 5 languages, block/report all present in the app</t>
         </is>
       </c>
       <c r="G131" s="10" t="inlineStr">
         <is>
-          <t>no claim: travel mode: True; no claim: incognito: True; no claim: swipe: True; no claim: video call: True; no claim: videocall: True; no claim: sign up with apple: True; no claim: google, or email: True</t>
+          <t>mbti_quiz: True; work_school_ui: True; face_verify_ui: True; 5 languages: 5</t>
         </is>
       </c>
       <c r="H131" s="11" t="inlineStr">
@@ -8853,7 +8851,7 @@
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>CLAIM-007</t>
+          <t>CLAIM-005</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
@@ -8863,48 +8861,46 @@
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>Copy consistency</t>
+          <t>Coverage audit</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>The app's own verification copy matches what the backend really enforces</t>
+          <t>App strengths that are really usable today are showcased on the website</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
         <is>
-          <t>compare mobile en.json banner text with blind_chat_service rules</t>
+          <t>keyword coverage of the English marketing copy</t>
         </is>
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
-          <t>if the app says identity verification is 'required to activate your account', unverified users must actually be blocked from Blind Chat</t>
+          <t>website mentions: instant translation, couple stories, icebreakers, AI match, free daily matches + membership, ID-checked badge</t>
         </is>
       </c>
       <c r="G132" s="10" t="inlineStr">
         <is>
-          <t>copy and enforcement agree: False (expected True)</t>
-        </is>
-      </c>
-      <c r="H132" s="12" t="inlineStr">
+          <t>website mentions instant translation: True; website mentions couple stories: True; website mentions icebreakers: True; website mentions AI match: True; website mentions free daily matches: True; website mentions membership: True; website mentions ID-checked badge: True; website mentions block / report: True</t>
+        </is>
+      </c>
+      <c r="H132" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I132" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="J132" s="10" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I132" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K132" s="10" t="n"/>
-      <c r="L132" s="10" t="inlineStr">
-        <is>
-          <t>app banner: 'Identity verification is required to activate your account'; face verification enforced by backend: False</t>
-        </is>
-      </c>
+      <c r="K132" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="L132" s="10" t="inlineStr"/>
       <c r="M132" s="10" t="n">
         <v>0</v>
       </c>
@@ -8912,37 +8908,37 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>WEB-005</t>
+          <t>CLAIM-006</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>웹사이트</t>
+          <t>웹↔앱 일치</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Brand consistency</t>
+          <t>Claim audit</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>The brand is spelled 'SooDaMate' in every language (no invented localized names)</t>
+          <t>Website does not advertise features that are hidden or absent in the current app</t>
         </is>
       </c>
       <c r="E133" s="10" t="inlineStr">
         <is>
-          <t>grep web/</t>
+          <t>grep English marketing copy for features removed from the app UI</t>
         </is>
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
-          <t>0 occurrences of made-up brand variants (数搭伴侣, 数多メイト, 수다 메이트) in i18n.js / html</t>
+          <t>no mention of travel mode, incognito, swipe/classic discovery, video calls, or sign-up via Apple/Google/email</t>
         </is>
       </c>
       <c r="G133" s="10" t="inlineStr">
         <is>
-          <t>occurrences of 数搭: 0; occurrences of 数多メイト: 0; occurrences of 수다 메이트: 0</t>
+          <t>no claim: travel mode: True; no claim: incognito: True; no claim: swipe: True; no claim: video call: True; no claim: videocall: True; no claim: sign up with apple: True; no claim: google, or email: True</t>
         </is>
       </c>
       <c r="H133" s="11" t="inlineStr">
@@ -8967,46 +8963,46 @@
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>UI-001</t>
+          <t>CLAIM-007</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>화면(앱)</t>
+          <t>웹↔앱 일치</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>Login screen</t>
+          <t>Copy consistency</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>First launch shows the phone-number sign-in in the default language (English)</t>
+          <t>The app's own verification copy matches what the backend really enforces</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>브라우저에서 직접 조작</t>
+          <t>compare mobile en.json banner text with blind_chat_service rules</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>Title SooDaMate, subtitle 'Just your phone number - nothing else needed', country chips South Korea (+82) / United States (+1), +82 prefix box, Send Code button</t>
+          <t>if the app says identity verification is 'required to activate your account', unverified users must actually be blocked from Blind Chat</t>
         </is>
       </c>
       <c r="G134" s="10" t="inlineStr">
         <is>
-          <t>SooDaMate / Just your phone number — nothing else needed / South Korea (+82) / United States (+1) / +82 / Send Code</t>
-        </is>
-      </c>
-      <c r="H134" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>copy and enforcement agree: False (expected True)</t>
+        </is>
+      </c>
+      <c r="H134" s="12" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I134" s="10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J134" s="10" t="inlineStr">
         <is>
@@ -9014,43 +9010,49 @@
         </is>
       </c>
       <c r="K134" s="10" t="n"/>
-      <c r="L134" s="10" t="inlineStr"/>
-      <c r="M134" s="10" t="n"/>
+      <c r="L134" s="10" t="inlineStr">
+        <is>
+          <t>app banner: 'Identity verification is required to activate your account'; face verification enforced by backend: False</t>
+        </is>
+      </c>
+      <c r="M134" s="10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>UI-002</t>
+          <t>WEB-005</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>화면(앱)</t>
+          <t>웹사이트</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>Login screen</t>
+          <t>Brand consistency</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>Typing a phone number auto-formats it (010-1234-5678 style)</t>
+          <t>The brand is spelled 'SooDaMate' in every language (no invented localized names)</t>
         </is>
       </c>
       <c r="E135" s="10" t="inlineStr">
         <is>
-          <t>브라우저에서 직접 조작</t>
+          <t>grep web/</t>
         </is>
       </c>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t>input shows hyphenated local format while typing</t>
+          <t>0 occurrences of made-up brand variants (数搭伴侣, 数多メイト, 수다 메이트) in i18n.js / html</t>
         </is>
       </c>
       <c r="G135" s="10" t="inlineStr">
         <is>
-          <t>typed 01512345678 -&gt; field value '015-1234-5678'</t>
+          <t>occurrences of 数搭: 0; occurrences of 数多メイト: 0; occurrences of 수다 메이트: 0</t>
         </is>
       </c>
       <c r="H135" s="11" t="inlineStr">
@@ -9068,42 +9070,44 @@
       </c>
       <c r="K135" s="10" t="n"/>
       <c r="L135" s="10" t="inlineStr"/>
-      <c r="M135" s="10" t="n"/>
+      <c r="M135" s="10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>UI-003</t>
+          <t>WEB-006</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>화면(앱)</t>
+          <t>웹사이트</t>
         </is>
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>Internet-number filter</t>
+          <t>Policy consistency</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>A number the server refuses (015-1234-5678, not a real mobile prefix) shows the localized 'no internet/virtual numbers' message</t>
+          <t>Terms, privacy policy, child-safety page and the safety card all describe the same 18+ gate in all 5 languages</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>브라우저에서 직접 조작</t>
+          <t>inspect the translations</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>red error text: Internet (VoIP) and virtual numbers aren't supported. Please use a real mobile number from a carrier.</t>
+          <t>each of terms.a2.body, privacy.s5, childSafety.s2.li1, safety.4.body mentions 18 and (for the first three) the blocked/disabled outcome in every language</t>
         </is>
       </c>
       <c r="G136" s="10" t="inlineStr">
         <is>
-          <t>Internet (VoIP) and virtual numbers aren't supported. Please use a real mobile number from a carrier. (shown above the country chips)</t>
+          <t>terms.a2.body [ko] mentions 18: True; terms.a2.body [en] mentions 18: True; terms.a2.body [es] mentions 18: True; terms.a2.body [zh] mentions 18: True; terms.a2.body [ja] mentions 18: True; privacy.s5 [ko] mentions 18: True; privacy.s5 [en] mentions 18: True; privacy.s5 [es] mentions 18: True; privacy.s5 [zh] mentions 18: True; privacy.s5 [ja] mentions 18: True; childSafety.s2.li1 [ko] mentions 18: True; childSafety.s2.li1 [en] mentions 18: True; childSafety.s2.li1 [es] mentions 18: True; childSafety.s2.li1 [zh] mentions 18: True; childSafety.s2.li1 [ja] mentions 18: True; safety.4.body [ko] mentions 18: True; safety.4.body [en] mentions 18: True; safety.4.body [es] mentions 18: True; safety.4.body [zh] mentions 18: True; safety.4.body [ja] mentions 18: True; privacy discloses the retained phone number (en): True; legal pages carry the new 'last updated' date: True</t>
         </is>
       </c>
       <c r="H136" s="11" t="inlineStr">
@@ -9121,12 +9125,14 @@
       </c>
       <c r="K136" s="10" t="n"/>
       <c r="L136" s="10" t="inlineStr"/>
-      <c r="M136" s="10" t="n"/>
+      <c r="M136" s="10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>UI-004</t>
+          <t>UI-001</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
@@ -9136,12 +9142,12 @@
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>Code entry</t>
+          <t>Login screen</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>After Send Code the code screen appears with number, countdown and actions</t>
+          <t>First launch shows the phone-number sign-in in the default language (English)</t>
         </is>
       </c>
       <c r="E137" s="10" t="inlineStr">
@@ -9151,12 +9157,12 @@
       </c>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>'Enter the code we texted you', 'We sent a code to +82…', 'Code expires in 09:5x', Verify / Resend code / Change number</t>
+          <t>Title SooDaMate, subtitle 'Just your phone number - nothing else needed', country chips South Korea (+82) / United States (+1), +82 prefix box, Send Code button</t>
         </is>
       </c>
       <c r="G137" s="10" t="inlineStr">
         <is>
-          <t>Enter the code we texted you / We sent a code to +821099990001 / Code expires in 09:58 / Verify / Resend code / Change number</t>
+          <t>SooDaMate / Just your phone number — nothing else needed / South Korea (+82) / United States (+1) / +82 / Send Code</t>
         </is>
       </c>
       <c r="H137" s="11" t="inlineStr">
@@ -9179,7 +9185,7 @@
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>UI-005</t>
+          <t>UI-002</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
@@ -9189,12 +9195,12 @@
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>Code entry</t>
+          <t>Login screen</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>Wrong code shows an error and keeps the user on the code screen</t>
+          <t>Typing a phone number auto-formats it (010-1234-5678 style)</t>
         </is>
       </c>
       <c r="E138" s="10" t="inlineStr">
@@ -9204,21 +9210,21 @@
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>clear, localized error message</t>
+          <t>input shows hyphenated local format while typing</t>
         </is>
       </c>
       <c r="G138" s="10" t="inlineStr">
         <is>
-          <t>'incorrect or expired code' (raw English server text; not localized in build 10) -&gt; fixed in source: now mapped to phoneAuth.incorrectCode in 5 languages (needs next app build)</t>
-        </is>
-      </c>
-      <c r="H138" s="12" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>typed 01512345678 -&gt; field value '015-1234-5678'</t>
+        </is>
+      </c>
+      <c r="H138" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I138" s="10" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J138" s="10" t="inlineStr">
         <is>
@@ -9232,7 +9238,7 @@
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>UI-006</t>
+          <t>UI-003</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
@@ -9242,12 +9248,12 @@
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Internet-number filter</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>Correct code logs in and lands on the Profile tab</t>
+          <t>A number the server refuses (015-1234-5678, not a real mobile prefix) shows the localized 'no internet/virtual numbers' message</t>
         </is>
       </c>
       <c r="E139" s="10" t="inlineStr">
@@ -9257,12 +9263,12 @@
       </c>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t>signed-in user sees own profile page with tab bar (Chat / Profile / center Blind button)</t>
+          <t>red error text: Internet (VoIP) and virtual numbers aren't supported. Please use a real mobile number from a carrier.</t>
         </is>
       </c>
       <c r="G139" s="10" t="inlineStr">
         <is>
-          <t>Profile screen: completeness %, name QA수다, 'Free member' pill, bio, '5 AI Match credits', 'Unlimited Matching active', perk explainer cards, Couple Stories card, Premium card, 'View purchase history', SooDaList cross-promo; tab bar Chat / Profile / Blind</t>
+          <t>Internet (VoIP) and virtual numbers aren't supported. Please use a real mobile number from a carrier. (shown above the country chips)</t>
         </is>
       </c>
       <c r="H139" s="11" t="inlineStr">
@@ -9285,7 +9291,7 @@
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>UI-007</t>
+          <t>UI-004</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
@@ -9295,12 +9301,12 @@
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>Profile / membership</t>
+          <t>Code entry</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>Membership status is visible (free vs premium) with credits and unlimited state</t>
+          <t>After Send Code the code screen appears with number, countdown and actions</t>
         </is>
       </c>
       <c r="E140" s="10" t="inlineStr">
@@ -9310,12 +9316,12 @@
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>pill shows Free member; AI Match credits count; Unlimited Matching on/off</t>
+          <t>'Enter the code we texted you', 'We sent a code to +82…', 'Code expires in 09:5x', Verify / Resend code / Change number</t>
         </is>
       </c>
       <c r="G140" s="10" t="inlineStr">
         <is>
-          <t>'Free member' pill; '5 AI Match credits'; 'Unlimited Matching active' (after top-up purchase); for a fresh user '0 AI Match credits / Unlimited Matching off'</t>
+          <t>Enter the code we texted you / We sent a code to +821099990001 / Code expires in 09:58 / Verify / Resend code / Change number</t>
         </is>
       </c>
       <c r="H140" s="11" t="inlineStr">
@@ -9338,7 +9344,7 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>UI-008</t>
+          <t>UI-005</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
@@ -9348,12 +9354,12 @@
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>Purchase history</t>
+          <t>Code entry</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>Purchase history page lists the purchases newest-first with dates</t>
+          <t>Wrong code shows an error and keeps the user on the code screen</t>
         </is>
       </c>
       <c r="E141" s="10" t="inlineStr">
@@ -9363,21 +9369,21 @@
       </c>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t>rows: Unlimited Matching - 1 week, AI Match x5 (5 credited) with dates</t>
+          <t>clear, localized error message</t>
         </is>
       </c>
       <c r="G141" s="10" t="inlineStr">
         <is>
-          <t>Purchase history / Unlimited Matching — 1 week / Unlimited Matching / September 20, 2026 / AI Match x5 / 5 credited / September 20, 2026</t>
-        </is>
-      </c>
-      <c r="H141" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>'incorrect or expired code' (raw English server text; not localized in build 10) -&gt; fixed in source: now mapped to phoneAuth.incorrectCode in 5 languages (needs next app build)</t>
+        </is>
+      </c>
+      <c r="H141" s="12" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I141" s="10" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J141" s="10" t="inlineStr">
         <is>
@@ -9391,7 +9397,7 @@
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
         <is>
-          <t>UI-009</t>
+          <t>UI-006</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
@@ -9401,12 +9407,12 @@
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>Chat list</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>Chat list shows the classic match (real name) and the blind match (masked name)</t>
+          <t>Correct code logs in and lands on the Profile tab</t>
         </is>
       </c>
       <c r="E142" s="10" t="inlineStr">
@@ -9416,12 +9422,12 @@
       </c>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t>rows 'QAuiMan' and 'Q***' each with 'Matched &lt;date&gt;'</t>
+          <t>signed-in user sees own profile page with tab bar (Chat / Profile / center Blind button)</t>
         </is>
       </c>
       <c r="G142" s="10" t="inlineStr">
         <is>
-          <t>Chats / Q*** / Matched 9/20/2026 / QAuiMan / Matched 9/20/2026</t>
+          <t>Profile screen: completeness %, name QA수다, 'Free member' pill, bio, '5 AI Match credits', 'Unlimited Matching active', perk explainer cards, Couple Stories card, Premium card, 'View purchase history', SooDaList cross-promo; tab bar Chat / Profile / Blind</t>
         </is>
       </c>
       <c r="H142" s="11" t="inlineStr">
@@ -9444,7 +9450,7 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>UI-010</t>
+          <t>UI-007</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
@@ -9454,12 +9460,12 @@
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>Chat room</t>
+          <t>Profile / membership</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>Chat room renders text, an image message, a translated message with 'View original', and sends new messages</t>
+          <t>Membership status is visible (free vs premium) with credits and unlimited state</t>
         </is>
       </c>
       <c r="E143" s="10" t="inlineStr">
@@ -9469,12 +9475,12 @@
       </c>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t>own Korean message; partner's English message shown translated to Korean with 'Translated · View original'; image message loads (800px); sending 'UI에서 보낸 메시지 테스트 ✅' appears and is stored</t>
+          <t>pill shows Free member; AI Match credits count; Unlimited Matching on/off</t>
         </is>
       </c>
       <c r="G143" s="10" t="inlineStr">
         <is>
-          <t>messages shown in order; 'Translated · View original' label present; image loaded (naturalWidth 800); typed message appeared after Send and was found in the DB (Messages table) for that match</t>
+          <t>'Free member' pill; '5 AI Match credits'; 'Unlimited Matching active' (after top-up purchase); for a fresh user '0 AI Match credits / Unlimited Matching off'</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr">
@@ -9497,7 +9503,7 @@
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
         <is>
-          <t>UI-011</t>
+          <t>UI-008</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
@@ -9507,12 +9513,12 @@
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>Blind chat room</t>
+          <t>Purchase history</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>Blind chat room hides identity and offers icebreaker + reveal</t>
+          <t>Purchase history page lists the purchases newest-first with dates</t>
         </is>
       </c>
       <c r="E144" s="10" t="inlineStr">
@@ -9522,12 +9528,12 @@
       </c>
       <c r="F144" s="10" t="inlineStr">
         <is>
-          <t>header 'Q***'; 'CONVERSATION STARTER' card; 'Matched on 🍜 Food'; 'Ask to reveal profiles'; after tapping: 'You asked to reveal profiles — waiting for a response'</t>
+          <t>rows: Unlimited Matching - 1 week, AI Match x5 (5 credited) with dates</t>
         </is>
       </c>
       <c r="G144" s="10" t="inlineStr">
         <is>
-          <t>Q*** / About Q*** / CONVERSATION STARTER / Why not break the ice and say hi? 😊 / Matched on 🍜 Food / Ask to reveal profiles -&gt; 'You asked to reveal profiles — waiting for a response'; icebreaker card disappears after the first message</t>
+          <t>Purchase history / Unlimited Matching — 1 week / Unlimited Matching / September 20, 2026 / AI Match x5 / 5 credited / September 20, 2026</t>
         </is>
       </c>
       <c r="H144" s="11" t="inlineStr">
@@ -9550,7 +9556,7 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>UI-012</t>
+          <t>UI-009</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
@@ -9560,12 +9566,12 @@
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>Face verification screen</t>
+          <t>Chat list</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>Unsubmitted state: explanation, selfie + ID slots, submit button</t>
+          <t>Chat list shows the classic match (real name) and the blind match (masked name)</t>
         </is>
       </c>
       <c r="E145" s="10" t="inlineStr">
@@ -9575,12 +9581,12 @@
       </c>
       <c r="F145" s="10" t="inlineStr">
         <is>
-          <t>Face verification screen with 'Take a selfie', 'Add a photo of your ID', 'Submit for review'</t>
+          <t>rows 'QAuiMan' and 'Q***' each with 'Matched &lt;date&gt;'</t>
         </is>
       </c>
       <c r="G145" s="10" t="inlineStr">
         <is>
-          <t>Face verification / 'Identity verification is required for a safer community…your account activates once it's approved.' / Selfie / Take a selfie / Photo ID / Add a photo of your ID / Submit for review</t>
+          <t>Chats / Q*** / Matched 9/20/2026 / QAuiMan / Matched 9/20/2026</t>
         </is>
       </c>
       <c r="H145" s="11" t="inlineStr">
@@ -9603,7 +9609,7 @@
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
         <is>
-          <t>UI-013</t>
+          <t>UI-010</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
@@ -9613,12 +9619,12 @@
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>Face verification screen</t>
+          <t>Chat room</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
-          <t>Pending state after submitting</t>
+          <t>Chat room renders text, an image message, a translated message with 'View original', and sends new messages</t>
         </is>
       </c>
       <c r="E146" s="10" t="inlineStr">
@@ -9628,12 +9634,12 @@
       </c>
       <c r="F146" s="10" t="inlineStr">
         <is>
-          <t>'Your selfie is being reviewed' notice</t>
+          <t>own Korean message; partner's English message shown translated to Korean with 'Translated · View original'; image message loads (800px); sending 'UI에서 보낸 메시지 테스트 ✅' appears and is stored</t>
         </is>
       </c>
       <c r="G146" s="10" t="inlineStr">
         <is>
-          <t>⏳ Your selfie is being reviewed — this usually doesn't take long. (form stays visible)</t>
+          <t>messages shown in order; 'Translated · View original' label present; image loaded (naturalWidth 800); typed message appeared after Send and was found in the DB (Messages table) for that match</t>
         </is>
       </c>
       <c r="H146" s="11" t="inlineStr">
@@ -9656,7 +9662,7 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>UI-014</t>
+          <t>UI-011</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
@@ -9666,12 +9672,12 @@
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>Face verification screen</t>
+          <t>Blind chat room</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>After the admin approves in the admin page, the app shows the verified state</t>
+          <t>Blind chat room hides identity and offers icebreaker + reveal</t>
         </is>
       </c>
       <c r="E147" s="10" t="inlineStr">
@@ -9681,12 +9687,12 @@
       </c>
       <c r="F147" s="10" t="inlineStr">
         <is>
-          <t>verification banner disappears and the verified badge image renders next to the name</t>
+          <t>header 'Q***'; 'CONVERSATION STARTER' card; 'Matched on 🍜 Food'; 'Ask to reveal profiles'; after tapping: 'You asked to reveal profiles — waiting for a response'</t>
         </is>
       </c>
       <c r="G147" s="10" t="inlineStr">
         <is>
-          <t>Banner gone (profile now says 'Finish filling out your profile'); verified-badge.png (512px) rendered; DB: face_verified=True, status=approved</t>
+          <t>Q*** / About Q*** / CONVERSATION STARTER / Why not break the ice and say hi? 😊 / Matched on 🍜 Food / Ask to reveal profiles -&gt; 'You asked to reveal profiles — waiting for a response'; icebreaker card disappears after the first message</t>
         </is>
       </c>
       <c r="H147" s="11" t="inlineStr">
@@ -9709,7 +9715,7 @@
     <row r="148">
       <c r="A148" s="10" t="inlineStr">
         <is>
-          <t>UI-015</t>
+          <t>UI-012</t>
         </is>
       </c>
       <c r="B148" s="10" t="inlineStr">
@@ -9724,7 +9730,7 @@
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>Rejected state shows the reason and a Resubmit button</t>
+          <t>Unsubmitted state: explanation, selfie + ID slots, submit button</t>
         </is>
       </c>
       <c r="E148" s="10" t="inlineStr">
@@ -9734,12 +9740,12 @@
       </c>
       <c r="F148" s="10" t="inlineStr">
         <is>
-          <t>banner 'Your identity verification was rejected — see why'; screen shows reason + Resubmit</t>
+          <t>Face verification screen with 'Take a selfie', 'Add a photo of your ID', 'Submit for review'</t>
         </is>
       </c>
       <c r="G148" s="10" t="inlineStr">
         <is>
-          <t>Profile banner: 'Your identity verification was rejected — see why'. Screen: 'Your last submission wasn't approved. Try again with a clear, well-lit selfie. / Reason: Your ID photo was blurry or unreadable.' / Resubmit</t>
+          <t>Face verification / 'Identity verification is required for a safer community…your account activates once it's approved.' / Selfie / Take a selfie / Photo ID / Add a photo of your ID / Submit for review</t>
         </is>
       </c>
       <c r="H148" s="11" t="inlineStr">
@@ -9762,7 +9768,7 @@
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>UI-016</t>
+          <t>UI-013</t>
         </is>
       </c>
       <c r="B149" s="10" t="inlineStr">
@@ -9772,12 +9778,12 @@
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>Copy consistency</t>
+          <t>Face verification screen</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>App copy says identity verification is required to activate the account</t>
+          <t>Pending state after submitting</t>
         </is>
       </c>
       <c r="E149" s="10" t="inlineStr">
@@ -9787,21 +9793,21 @@
       </c>
       <c r="F149" s="10" t="inlineStr">
         <is>
-          <t>copy matches real behaviour</t>
+          <t>'Your selfie is being reviewed' notice</t>
         </is>
       </c>
       <c r="G149" s="10" t="inlineStr">
         <is>
-          <t>Banner/screen say 'required to activate your account', but the backend lets unverified users use Blind Chat -&gt; inconsistency (see CLAIM-007, open product decision)</t>
-        </is>
-      </c>
-      <c r="H149" s="12" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>⏳ Your selfie is being reviewed — this usually doesn't take long. (form stays visible)</t>
+        </is>
+      </c>
+      <c r="H149" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I149" s="10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J149" s="10" t="inlineStr">
         <is>
@@ -9815,22 +9821,22 @@
     <row r="150">
       <c r="A150" s="10" t="inlineStr">
         <is>
-          <t>UI-017</t>
+          <t>UI-014</t>
         </is>
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>화면(관리자)</t>
+          <t>화면(앱)</t>
         </is>
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>Face verification review page</t>
+          <t>Face verification screen</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>Admin signs in with email + password and sees pending submissions with real images</t>
+          <t>After the admin approves in the admin page, the app shows the verified state</t>
         </is>
       </c>
       <c r="E150" s="10" t="inlineStr">
@@ -9840,12 +9846,12 @@
       </c>
       <c r="F150" s="10" t="inlineStr">
         <is>
-          <t>tabs Pending / Approved / Rejected; each card shows Selfie + ID images, name, submit time, Approve / Reject</t>
+          <t>verification banner disappears and the verified badge image renders next to the name</t>
         </is>
       </c>
       <c r="G150" s="10" t="inlineStr">
         <is>
-          <t>Face verification review / Pending / Approved / Rejected / card: QA심사대기 with two images (720x900 selfie, 900x560 ID, both loaded from signed R2 URLs) + Approve / Reject</t>
+          <t>Banner gone (profile now says 'Finish filling out your profile'); verified-badge.png (512px) rendered; DB: face_verified=True, status=approved</t>
         </is>
       </c>
       <c r="H150" s="11" t="inlineStr">
@@ -9868,22 +9874,22 @@
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>UI-018</t>
+          <t>UI-015</t>
         </is>
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>화면(관리자)</t>
+          <t>화면(앱)</t>
         </is>
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Face verification review page</t>
+          <t>Face verification screen</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>Approve button approves and moves the item to the Approved tab</t>
+          <t>Rejected state shows the reason and a Resubmit button</t>
         </is>
       </c>
       <c r="E151" s="10" t="inlineStr">
@@ -9893,12 +9899,12 @@
       </c>
       <c r="F151" s="10" t="inlineStr">
         <is>
-          <t>Pending list becomes 'Nothing here.'; Approved tab lists the person as approved</t>
+          <t>banner 'Your identity verification was rejected — see why'; screen shows reason + Resubmit</t>
         </is>
       </c>
       <c r="G151" s="10" t="inlineStr">
         <is>
-          <t>After clicking Approve: Pending -&gt; 'Nothing here.'; Approved tab: QA심사대기 … approved</t>
+          <t>Profile banner: 'Your identity verification was rejected — see why'. Screen: 'Your last submission wasn't approved. Try again with a clear, well-lit selfie. / Reason: Your ID photo was blurry or unreadable.' / Resubmit</t>
         </is>
       </c>
       <c r="H151" s="11" t="inlineStr">
@@ -9921,22 +9927,22 @@
     <row r="152">
       <c r="A152" s="10" t="inlineStr">
         <is>
-          <t>UI-019</t>
+          <t>UI-016</t>
         </is>
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>화면(관리자)</t>
+          <t>화면(앱)</t>
         </is>
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>Face verification review page</t>
+          <t>Copy consistency</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>Reject opens a reason dropdown (7 options) and confirm moves it to Rejected with the reason</t>
+          <t>App copy says identity verification is required to activate the account</t>
         </is>
       </c>
       <c r="E152" s="10" t="inlineStr">
@@ -9946,21 +9952,21 @@
       </c>
       <c r="F152" s="10" t="inlineStr">
         <is>
-          <t>dropdown: selfie/ID mismatch, ID blurry, selfie blurry, name mismatch, ID invalid, incomplete, other (custom); Confirm reject / Cancel; Rejected tab shows the reason</t>
+          <t>copy matches real behaviour</t>
         </is>
       </c>
       <c r="G152" s="10" t="inlineStr">
         <is>
-          <t>7 options exactly as expected; chose 'ID photo is blurry or unreadable' -&gt; Rejected tab: QA거절UI … rejected "ID photo is blurry or unreadable"</t>
-        </is>
-      </c>
-      <c r="H152" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Banner/screen say 'required to activate your account', but the backend lets unverified users use Blind Chat -&gt; inconsistency (see CLAIM-007, open product decision)</t>
+        </is>
+      </c>
+      <c r="H152" s="12" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I152" s="10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J152" s="10" t="inlineStr">
         <is>
@@ -9974,22 +9980,22 @@
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>UI-020</t>
+          <t>UI-017</t>
         </is>
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>화면(웹사이트)</t>
+          <t>화면(관리자)</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>Language dropdown</t>
+          <t>Face verification review page</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>Website defaults to English and offers 5 languages with flags in a dropdown</t>
+          <t>Admin signs in with email + password and sees pending submissions with real images</t>
         </is>
       </c>
       <c r="E153" s="10" t="inlineStr">
@@ -9999,12 +10005,12 @@
       </c>
       <c r="F153" s="10" t="inlineStr">
         <is>
-          <t>html lang=en, trigger shows 🇺🇸, 5 options (한국어/English/Español/中文/日本語)</t>
+          <t>tabs Pending / Approved / Rejected; each card shows Selfie + ID images, name, submit time, Approve / Reject</t>
         </is>
       </c>
       <c r="G153" s="10" t="inlineStr">
         <is>
-          <t>html lang=en; trigger '🇺🇸 ▾'; 5 language options present in the menu</t>
+          <t>Face verification review / Pending / Approved / Rejected / card: QA심사대기 with two images (720x900 selfie, 900x560 ID, both loaded from signed R2 URLs) + Approve / Reject</t>
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr">
@@ -10027,22 +10033,22 @@
     <row r="154">
       <c r="A154" s="10" t="inlineStr">
         <is>
-          <t>UI-021</t>
+          <t>UI-018</t>
         </is>
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>화면(웹사이트)</t>
+          <t>화면(관리자)</t>
         </is>
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>Translations</t>
+          <t>Face verification review page</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>Each of the 5 languages renders the full home page without leaking Korean into other languages</t>
+          <t>Approve button approves and moves the item to the Approved tab</t>
         </is>
       </c>
       <c r="E154" s="10" t="inlineStr">
@@ -10052,12 +10058,12 @@
       </c>
       <c r="F154" s="10" t="inlineStr">
         <is>
-          <t>hero + 8 feature cards translated in en/ko/es/zh/ja; no Hangul in non-Korean pages</t>
+          <t>Pending list becomes 'Nothing here.'; Approved tab lists the person as approved</t>
         </is>
       </c>
       <c r="G154" s="10" t="inlineStr">
         <is>
-          <t>All 5 languages rendered 8 feature cards (Blind Chat, AI Match, Icebreakers, Couple Stories, 5 free matches, Real-time chat+translation, Work &amp; school, ID badge); 0 Hangul strings left in en/es/zh/ja</t>
+          <t>After clicking Approve: Pending -&gt; 'Nothing here.'; Approved tab: QA심사대기 … approved</t>
         </is>
       </c>
       <c r="H154" s="11" t="inlineStr">
@@ -10080,22 +10086,22 @@
     <row r="155">
       <c r="A155" s="10" t="inlineStr">
         <is>
-          <t>UI-022</t>
+          <t>UI-019</t>
         </is>
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>화면(웹사이트)</t>
+          <t>화면(관리자)</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>Layout / responsive</t>
+          <t>Face verification review page</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>Horizontal overflow and visual spacing on phone width</t>
+          <t>Reject opens a reason dropdown (7 options) and confirm moves it to Rejected with the reason</t>
         </is>
       </c>
       <c r="E155" s="10" t="inlineStr">
@@ -10105,20 +10111,22 @@
       </c>
       <c r="F155" s="10" t="inlineStr">
         <is>
-          <t>no horizontal scroll at 375px</t>
+          <t>dropdown: selfie/ID mismatch, ID blurry, selfie blurry, name mismatch, ID invalid, incomplete, other (custom); Confirm reject / Cancel; Rejected tab shows the reason</t>
         </is>
       </c>
       <c r="G155" s="10" t="inlineStr">
         <is>
-          <t>Not measurable: the Browser pane was not displayed, so the page reported a 0x0 viewport. CSS uses auto-fit grids; needs a visual pass on a real device.</t>
-        </is>
-      </c>
-      <c r="H155" s="13" t="inlineStr">
-        <is>
-          <t>N/T</t>
-        </is>
-      </c>
-      <c r="I155" s="10" t="n"/>
+          <t>7 options exactly as expected; chose 'ID photo is blurry or unreadable' -&gt; Rejected tab: QA거절UI … rejected "ID photo is blurry or unreadable"</t>
+        </is>
+      </c>
+      <c r="H155" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I155" s="10" t="n">
+        <v>100</v>
+      </c>
       <c r="J155" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -10131,22 +10139,22 @@
     <row r="156">
       <c r="A156" s="10" t="inlineStr">
         <is>
-          <t>UI-023</t>
+          <t>UI-020</t>
         </is>
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>화면(관리자)</t>
+          <t>화면(웹사이트)</t>
         </is>
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Language dropdown</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>Admin dashboard shows platform statistics</t>
+          <t>Website defaults to English and offers 5 languages with flags in a dropdown</t>
         </is>
       </c>
       <c r="E156" s="10" t="inlineStr">
@@ -10156,12 +10164,12 @@
       </c>
       <c r="F156" s="10" t="inlineStr">
         <is>
-          <t>counters for users, new signups (today/7d/30d), open reports, banned users, pending verifications, new inquiries, active matches, messages today, premium users, 30-day revenue</t>
+          <t>html lang=en, trigger shows 🇺🇸, 5 options (한국어/English/Español/中文/日本語)</t>
         </is>
       </c>
       <c r="G156" s="10" t="inlineStr">
         <is>
-          <t>SooDaMate Admin dashboard: 전체 유저 / 오늘·7일·30일 신규가입 / 오픈 신고 / 정지된 유저 / 대기중 본인인증 / 신규 문의 / 활성 매칭 / 오늘 메시지 / 프리미엄 유저 / 30일 매출 ($10.98 = the two QA purchases at that moment) + 30-day signup chart</t>
+          <t>html lang=en; trigger '🇺🇸 ▾'; 5 language options present in the menu</t>
         </is>
       </c>
       <c r="H156" s="11" t="inlineStr">
@@ -10184,22 +10192,22 @@
     <row r="157">
       <c r="A157" s="10" t="inlineStr">
         <is>
-          <t>UI-024</t>
+          <t>UI-021</t>
         </is>
       </c>
       <c r="B157" s="10" t="inlineStr">
         <is>
-          <t>화면(관리자)</t>
+          <t>화면(웹사이트)</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>Report management</t>
+          <t>Translations</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>Report list, detail (reporter -&gt; reported, reason, detail, conversation) and the Warn action</t>
+          <t>Each of the 5 languages renders the full home page without leaking Korean into other languages</t>
         </is>
       </c>
       <c r="E157" s="10" t="inlineStr">
@@ -10209,12 +10217,12 @@
       </c>
       <c r="F157" s="10" t="inlineStr">
         <is>
-          <t>report row appears as open; detail shows reason/detail and conversation state; 경고 moves it to the 'warned' tab</t>
+          <t>hero + 8 feature cards translated in en/ko/es/zh/ja; no Hangul in non-Korean pages</t>
         </is>
       </c>
       <c r="G157" s="10" t="inlineStr">
         <is>
-          <t>Row 'QA수다 -&gt; QAuiTroll / 부적절한 메시지 / open'; detail modal: 'QA 신고 테스트' + '두 사람 사이에 대화 기록이 없어요.' + 경고/영구정지/기각/닫기; after 경고: gone from 열림, present in 경고됨 as 'warned'</t>
+          <t>All 5 languages rendered 8 feature cards (Blind Chat, AI Match, Icebreakers, Couple Stories, 5 free matches, Real-time chat+translation, Work &amp; school, ID badge); 0 Hangul strings left in en/es/zh/ja</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr">
@@ -10237,22 +10245,22 @@
     <row r="158">
       <c r="A158" s="10" t="inlineStr">
         <is>
-          <t>UI-025</t>
+          <t>UI-022</t>
         </is>
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>화면(관리자)</t>
+          <t>화면(웹사이트)</t>
         </is>
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>Inquiry management</t>
+          <t>Layout / responsive</t>
         </is>
       </c>
       <c r="D158" s="10" t="inlineStr">
         <is>
-          <t>Inquiry list -&gt; open (auto marks read) -&gt; resolve</t>
+          <t>Horizontal overflow and visual spacing on phone width</t>
         </is>
       </c>
       <c r="E158" s="10" t="inlineStr">
@@ -10262,22 +10270,20 @@
       </c>
       <c r="F158" s="10" t="inlineStr">
         <is>
-          <t>new inquiry visible; opening marks it read; '해결 처리' moves it to 처리완료</t>
+          <t>no horizontal scroll at 375px</t>
         </is>
       </c>
       <c r="G158" s="10" t="inlineStr">
         <is>
-          <t>Row 'QA수다 / QA 문의 / new'; detail shows the message text with emoji; 신규 tab empty afterwards; 처리완료 tab shows it as 'resolved'</t>
-        </is>
-      </c>
-      <c r="H158" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I158" s="10" t="n">
-        <v>100</v>
-      </c>
+          <t>Not measurable: the Browser pane was not displayed, so the page reported a 0x0 viewport. CSS uses auto-fit grids; needs a visual pass on a real device.</t>
+        </is>
+      </c>
+      <c r="H158" s="13" t="inlineStr">
+        <is>
+          <t>N/T</t>
+        </is>
+      </c>
+      <c r="I158" s="10" t="n"/>
       <c r="J158" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -10290,7 +10296,7 @@
     <row r="159">
       <c r="A159" s="10" t="inlineStr">
         <is>
-          <t>UI-026</t>
+          <t>UI-023</t>
         </is>
       </c>
       <c r="B159" s="10" t="inlineStr">
@@ -10300,12 +10306,12 @@
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>Promotions</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>Promotions tab lists products with prices and the active discount; starting a discount broadcasts a push to every user</t>
+          <t>Admin dashboard shows platform statistics</t>
         </is>
       </c>
       <c r="E159" s="10" t="inlineStr">
@@ -10315,12 +10321,12 @@
       </c>
       <c r="F159" s="10" t="inlineStr">
         <is>
-          <t>product dropdown with 6 products + prices, warning text about the push broadcast, list of promotions with 중지 button</t>
+          <t>counters for users, new signups (today/7d/30d), open reports, banned users, pending verifications, new inquiries, active matches, messages today, premium users, 30-day revenue</t>
         </is>
       </c>
       <c r="G159" s="10" t="inlineStr">
         <is>
-          <t>6 products with prices; warning '할인을 시작하면 등록된 모든 사용자에게 즉시 푸시 알림이 발송돼요'; the owner's real -50% AI Match x1 promotion (active since 2026-09-20 01:29) is listed. NOT clicked: starting a promotion would push to real users.</t>
+          <t>SooDaMate Admin dashboard: 전체 유저 / 오늘·7일·30일 신규가입 / 오픈 신고 / 정지된 유저 / 대기중 본인인증 / 신규 문의 / 활성 매칭 / 오늘 메시지 / 프리미엄 유저 / 30일 매출 ($10.98 = the two QA purchases at that moment) + 30-day signup chart</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr">
@@ -10343,22 +10349,22 @@
     <row r="160">
       <c r="A160" s="10" t="inlineStr">
         <is>
-          <t>UI-027</t>
+          <t>UI-024</t>
         </is>
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>화면(웹사이트)</t>
+          <t>화면(관리자)</t>
         </is>
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>Shop page</t>
+          <t>Report management</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>Shop page renders products, live prices and the active discount in the selected language</t>
+          <t>Report list, detail (reporter -&gt; reported, reason, detail, conversation) and the Warn action</t>
         </is>
       </c>
       <c r="E160" s="10" t="inlineStr">
@@ -10368,12 +10374,12 @@
       </c>
       <c r="F160" s="10" t="inlineStr">
         <is>
-          <t>6 product cards in Korean after choosing 한국어; strike-through price + -50% badge on the discounted product; Buy buttons disabled without an app login token</t>
+          <t>report row appears as open; detail shows reason/detail and conversation state; 경고 moves it to the 'warned' tab</t>
         </is>
       </c>
       <c r="G160" s="10" t="inlineStr">
         <is>
-          <t>ko: 'AI 매칭권 1회 ... $1.99 $1.00 -50% 구매', 'AI 매칭권 5회', '무제한 매칭 1주일/1개월', '프리미엄 멤버십 ... $9.99 · 매달 결제 / $99.99 · 매년 결제'; without a token the page says the login was not found and Buy is disabled</t>
+          <t>Row 'QA수다 -&gt; QAuiTroll / 부적절한 메시지 / open'; detail modal: 'QA 신고 테스트' + '두 사람 사이에 대화 기록이 없어요.' + 경고/영구정지/기각/닫기; after 경고: gone from 열림, present in 경고됨 as 'warned'</t>
         </is>
       </c>
       <c r="H160" s="11" t="inlineStr">
@@ -10393,8 +10399,430 @@
       <c r="L160" s="10" t="inlineStr"/>
       <c r="M160" s="10" t="n"/>
     </row>
+    <row r="161">
+      <c r="A161" s="10" t="inlineStr">
+        <is>
+          <t>UI-025</t>
+        </is>
+      </c>
+      <c r="B161" s="10" t="inlineStr">
+        <is>
+          <t>화면(관리자)</t>
+        </is>
+      </c>
+      <c r="C161" s="10" t="inlineStr">
+        <is>
+          <t>Inquiry management</t>
+        </is>
+      </c>
+      <c r="D161" s="10" t="inlineStr">
+        <is>
+          <t>Inquiry list -&gt; open (auto marks read) -&gt; resolve</t>
+        </is>
+      </c>
+      <c r="E161" s="10" t="inlineStr">
+        <is>
+          <t>브라우저에서 직접 조작</t>
+        </is>
+      </c>
+      <c r="F161" s="10" t="inlineStr">
+        <is>
+          <t>new inquiry visible; opening marks it read; '해결 처리' moves it to 처리완료</t>
+        </is>
+      </c>
+      <c r="G161" s="10" t="inlineStr">
+        <is>
+          <t>Row 'QA수다 / QA 문의 / new'; detail shows the message text with emoji; 신규 tab empty afterwards; 처리완료 tab shows it as 'resolved'</t>
+        </is>
+      </c>
+      <c r="H161" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I161" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="J161" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="10" t="n"/>
+      <c r="L161" s="10" t="inlineStr"/>
+      <c r="M161" s="10" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="10" t="inlineStr">
+        <is>
+          <t>UI-026</t>
+        </is>
+      </c>
+      <c r="B162" s="10" t="inlineStr">
+        <is>
+          <t>화면(관리자)</t>
+        </is>
+      </c>
+      <c r="C162" s="10" t="inlineStr">
+        <is>
+          <t>Promotions</t>
+        </is>
+      </c>
+      <c r="D162" s="10" t="inlineStr">
+        <is>
+          <t>Promotions tab lists products with prices and the active discount; starting a discount broadcasts a push to every user</t>
+        </is>
+      </c>
+      <c r="E162" s="10" t="inlineStr">
+        <is>
+          <t>브라우저에서 직접 조작</t>
+        </is>
+      </c>
+      <c r="F162" s="10" t="inlineStr">
+        <is>
+          <t>product dropdown with 6 products + prices, warning text about the push broadcast, list of promotions with 중지 button</t>
+        </is>
+      </c>
+      <c r="G162" s="10" t="inlineStr">
+        <is>
+          <t>6 products with prices; warning '할인을 시작하면 등록된 모든 사용자에게 즉시 푸시 알림이 발송돼요'; the owner's real -50% AI Match x1 promotion (active since 2026-09-20 01:29) is listed. NOT clicked: starting a promotion would push to real users.</t>
+        </is>
+      </c>
+      <c r="H162" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I162" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="J162" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="10" t="n"/>
+      <c r="L162" s="10" t="inlineStr"/>
+      <c r="M162" s="10" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="10" t="inlineStr">
+        <is>
+          <t>UI-027</t>
+        </is>
+      </c>
+      <c r="B163" s="10" t="inlineStr">
+        <is>
+          <t>화면(웹사이트)</t>
+        </is>
+      </c>
+      <c r="C163" s="10" t="inlineStr">
+        <is>
+          <t>Shop page</t>
+        </is>
+      </c>
+      <c r="D163" s="10" t="inlineStr">
+        <is>
+          <t>Shop page renders products, live prices and the active discount in the selected language</t>
+        </is>
+      </c>
+      <c r="E163" s="10" t="inlineStr">
+        <is>
+          <t>브라우저에서 직접 조작</t>
+        </is>
+      </c>
+      <c r="F163" s="10" t="inlineStr">
+        <is>
+          <t>6 product cards in Korean after choosing 한국어; strike-through price + -50% badge on the discounted product; Buy buttons disabled without an app login token</t>
+        </is>
+      </c>
+      <c r="G163" s="10" t="inlineStr">
+        <is>
+          <t>ko: 'AI 매칭권 1회 ... $1.99 $1.00 -50% 구매', 'AI 매칭권 5회', '무제한 매칭 1주일/1개월', '프리미엄 멤버십 ... $9.99 · 매달 결제 / $99.99 · 매년 결제'; without a token the page says the login was not found and Buy is disabled</t>
+        </is>
+      </c>
+      <c r="H163" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I163" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="J163" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="10" t="n"/>
+      <c r="L163" s="10" t="inlineStr"/>
+      <c r="M163" s="10" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="10" t="inlineStr">
+        <is>
+          <t>UI-028</t>
+        </is>
+      </c>
+      <c r="B164" s="10" t="inlineStr">
+        <is>
+          <t>화면(앱)</t>
+        </is>
+      </c>
+      <c r="C164" s="10" t="inlineStr">
+        <is>
+          <t>Age gate (new)</t>
+        </is>
+      </c>
+      <c r="D164" s="10" t="inlineStr">
+        <is>
+          <t>Sign-up form has an explicit, required 18+ confirmation</t>
+        </is>
+      </c>
+      <c r="E164" s="10" t="inlineStr">
+        <is>
+          <t>브라우저에서 직접 조작</t>
+        </is>
+      </c>
+      <c r="F164" s="10" t="inlineStr">
+        <is>
+          <t>checkbox 'I confirm that I am 18 years of age or older *' under the birth-date fields</t>
+        </is>
+      </c>
+      <c r="G164" s="10" t="inlineStr">
+        <is>
+          <t>Birth date * / Year / Month / Day / I confirm that I am 18 years of age or older * (checkbox row, red star = required)</t>
+        </is>
+      </c>
+      <c r="H164" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I164" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="J164" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="10" t="n"/>
+      <c r="L164" s="10" t="inlineStr"/>
+      <c r="M164" s="10" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="10" t="inlineStr">
+        <is>
+          <t>UI-029</t>
+        </is>
+      </c>
+      <c r="B165" s="10" t="inlineStr">
+        <is>
+          <t>화면(앱)</t>
+        </is>
+      </c>
+      <c r="C165" s="10" t="inlineStr">
+        <is>
+          <t>Age gate (new)</t>
+        </is>
+      </c>
+      <c r="D165" s="10" t="inlineStr">
+        <is>
+          <t>Birth-year dropdown offers under-18 years instead of hiding them</t>
+        </is>
+      </c>
+      <c r="E165" s="10" t="inlineStr">
+        <is>
+          <t>브라우저에서 직접 조작</t>
+        </is>
+      </c>
+      <c r="F165" s="10" t="inlineStr">
+        <is>
+          <t>years listed from age 10 upward so a minor can actually pick their year (and be blocked)</t>
+        </is>
+      </c>
+      <c r="G165" s="10" t="inlineStr">
+        <is>
+          <t>Dropdown starts at 2016 (age 10) and runs 2016, 2015, 2014 … 2007 …</t>
+        </is>
+      </c>
+      <c r="H165" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I165" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="J165" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="10" t="n"/>
+      <c r="L165" s="10" t="inlineStr"/>
+      <c r="M165" s="10" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="10" t="inlineStr">
+        <is>
+          <t>UI-030</t>
+        </is>
+      </c>
+      <c r="B166" s="10" t="inlineStr">
+        <is>
+          <t>화면(앱)</t>
+        </is>
+      </c>
+      <c r="C166" s="10" t="inlineStr">
+        <is>
+          <t>Age gate (new)</t>
+        </is>
+      </c>
+      <c r="D166" s="10" t="inlineStr">
+        <is>
+          <t>Choosing an under-18 birth date immediately shows the block screen</t>
+        </is>
+      </c>
+      <c r="E166" s="10" t="inlineStr">
+        <is>
+          <t>브라우저에서 직접 조작</t>
+        </is>
+      </c>
+      <c r="F166" s="10" t="inlineStr">
+        <is>
+          <t>full-screen block: title, explanation, support contact, OK button; no way to change the date</t>
+        </is>
+      </c>
+      <c r="G166" s="10" t="inlineStr">
+        <is>
+          <t>Picked 2012-06-05 -&gt; 'You must be 18 or older / SooDaMate is only available to adults. We can't create an account for you with this number. If you entered your birth date by mistake, contact support@soodamate.com. / OK'</t>
+        </is>
+      </c>
+      <c r="H166" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I166" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="J166" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="10" t="n"/>
+      <c r="L166" s="10" t="inlineStr"/>
+      <c r="M166" s="10" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="10" t="inlineStr">
+        <is>
+          <t>UI-031</t>
+        </is>
+      </c>
+      <c r="B167" s="10" t="inlineStr">
+        <is>
+          <t>화면(앱)</t>
+        </is>
+      </c>
+      <c r="C167" s="10" t="inlineStr">
+        <is>
+          <t>Age gate (new)</t>
+        </is>
+      </c>
+      <c r="D167" s="10" t="inlineStr">
+        <is>
+          <t>After OK the same phone number cannot register again</t>
+        </is>
+      </c>
+      <c r="E167" s="10" t="inlineStr">
+        <is>
+          <t>브라우저에서 직접 조작</t>
+        </is>
+      </c>
+      <c r="F167" s="10" t="inlineStr">
+        <is>
+          <t>OK returns to the login screen; logging in again with that number is refused with a localized 'account restricted' message</t>
+        </is>
+      </c>
+      <c r="G167" s="10" t="inlineStr">
+        <is>
+          <t>OK -&gt; login screen; same number + code -&gt; 'This account has been restricted. Please contact support if you need help.'; server: account is_active=False (AGE-001)</t>
+        </is>
+      </c>
+      <c r="H167" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I167" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="J167" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="10" t="n"/>
+      <c r="L167" s="10" t="inlineStr"/>
+      <c r="M167" s="10" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="10" t="inlineStr">
+        <is>
+          <t>UI-032</t>
+        </is>
+      </c>
+      <c r="B168" s="10" t="inlineStr">
+        <is>
+          <t>화면(앱)</t>
+        </is>
+      </c>
+      <c r="C168" s="10" t="inlineStr">
+        <is>
+          <t>Age gate (new)</t>
+        </is>
+      </c>
+      <c r="D168" s="10" t="inlineStr">
+        <is>
+          <t>Submitting the form without ticking the 18+ box shows the 'please confirm' message</t>
+        </is>
+      </c>
+      <c r="E168" s="10" t="inlineStr">
+        <is>
+          <t>브라우저에서 직접 조작</t>
+        </is>
+      </c>
+      <c r="F168" s="10" t="inlineStr">
+        <is>
+          <t>'Please confirm that you are 18 or older to continue' in the error list and the checkbox turns red</t>
+        </is>
+      </c>
+      <c r="G168" s="10" t="inlineStr">
+        <is>
+          <t>Not clicked in the browser walk-through (validation code and translations are type-checked and present in all 5 languages)</t>
+        </is>
+      </c>
+      <c r="H168" s="13" t="inlineStr">
+        <is>
+          <t>N/T</t>
+        </is>
+      </c>
+      <c r="I168" s="10" t="n"/>
+      <c r="J168" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="10" t="n"/>
+      <c r="L168" s="10" t="inlineStr"/>
+      <c r="M168" s="10" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M160"/>
+  <autoFilter ref="A1:M168"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10405,7 +10833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11265,8 +11693,55 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>D-18</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>연령 확인</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>수정 완료(빌드·배포 필요)</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>앱에 명시적인 '18세 이상 확인'과 '18세 미만 차단' 화면이 없었음 (Stripe 심사 요구사항)</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>출생연도 목록에서 18세 미만 연도를 숨기기만 해서 미성년자는 그냥 선택지가 없었고, 확인 체크도 차단 안내도 없었습니다. 같은 번호로 다른 생년월일을 다시 넣어 재시도하는 것도 막을 방법이 없었음.</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>필수 18+ 확인 체크박스 추가, 출생연도 목록에 10세부터 표시, 18세 미만 선택 시 즉시 차단 화면(문의처 안내) + 서버가 계정을 비활성화(POST /account/age-restricted)해 같은 번호로 재가입 불가. 이용약관·개인정보처리방침·아동안전 페이지·웹 안전 카드 문구를 5개 언어로 함께 수정(개인정보처리방침에는 차단된 가입의 전화번호 보관 사실 명시).</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>AGE-001, AGE-002, UI-028, UI-029, UI-030, UI-031, WEB-006</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>AGE-001: PASS 100.0%, AGE-002: PASS 100.0%, UI-028: PASS 100%, UI-029: PASS 100%, UI-030: PASS 100%, UI-031: PASS 100%, WEB-006: PASS 100.0%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I18"/>
+  <autoFilter ref="A1:I19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
